--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2553,6 +2554,255 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>소사업 월별 누적 - 2026-06 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>객실수 기준</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>OTA</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>G-OTA</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>소사업(백만)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>누계(백만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1월</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>온북</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>836.4</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>287.3</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>139.3</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>1263</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>온북</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1102.3</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>400.6</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>214.3</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1717.3</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>2980.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3월</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>온북</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>430.5</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>193.3</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>808.3</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>3788.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4월</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>온북</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>740.2</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>224.1</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>261.9</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1226.2</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>5014.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5월</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>온북</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>812.2</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>182</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>157.7</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>1151.9</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>6166.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6월</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RM FCST</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>892.8</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>1339.2</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>7505.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>누계</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="7" t="n">
+        <v>4814.3</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1596.9</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>1094.7</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>7505.9</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>7505.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2616,7 +2866,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>d08238c0-_______________5______________________260602_12.xlsx</t>
+          <t>소사업_전년비율_소스_2025.xlsx</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>8960</v>
+        <v>9295</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>124.2</v>
+        <v>130.8</v>
       </c>
       <c r="D3" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>2.6</v>
       </c>
-      <c r="E3" s="4" t="n">
-        <v>2.4</v>
-      </c>
       <c r="F3" s="4" t="n">
-        <v>129.3</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="4">
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>844</v>
+        <v>764</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0.5</v>
@@ -554,7 +554,7 @@
         <v>0.2</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="5">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>7.4</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1850</v>
+        <v>1800</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>9.5</v>
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>0.1</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>630</v>
+        <v>670</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0.3</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7066</v>
+        <v>7014</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>71.3</v>
+        <v>69.5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>89.3</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3000</v>
+        <v>3180</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>43.9</v>
+        <v>47.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>56.7</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6413</v>
+        <v>6763</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>57.3</v>
+        <v>62.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>21.2</v>
+        <v>21.6</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>79.8</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4329</v>
+        <v>4269</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>81.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>18.6</v>
+        <v>17.8</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>101</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2682</v>
+        <v>2742</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0.6</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="14">
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>11</v>
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2610</v>
+        <v>2710</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>80.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>18.2</v>
+        <v>20.6</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>98.5</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2900</v>
+        <v>3010</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>107.3</v>
+        <v>116.9</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>130.3</v>
+        <v>139.6</v>
       </c>
     </row>
     <row r="17">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1248</v>
+        <v>1222</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>59.7</v>
+        <v>55.8</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>84</v>
@@ -840,7 +840,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>144.3</v>
+        <v>140.4</v>
       </c>
     </row>
     <row r="18">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2752</v>
+        <v>2802</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>76.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>19.4</v>
@@ -862,7 +862,7 @@
         <v>0.1</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>96.09999999999999</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4472</v>
+        <v>4642</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>23.2</v>
+        <v>24.8</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>13.9</v>
@@ -884,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>37.1</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2584</v>
+        <v>2824</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>14.9</v>
+        <v>16.8</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>23.6</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1360</v>
+        <v>1490</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>18.5</v>
+        <v>20.1</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>17.7</v>
+        <v>19.5</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>36.4</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6500</v>
+        <v>5750</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>92.3</v>
+        <v>75.3</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>104.4</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2941</v>
+        <v>3032</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>20.4</v>
+        <v>21.2</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>37.5</v>
+        <v>36.6</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>75.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3450</v>
+        <v>3570</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>32</v>
+        <v>34.2</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>7.7</v>
@@ -994,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>39.7</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1210</v>
+        <v>1285</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>10.1</v>
+        <v>11.3</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>14.8</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>70699</v>
+        <v>71700</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>892.8</v>
+        <v>920.5</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>309.5</v>
+        <v>315.9</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>137</v>
+        <v>119.3</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1339.2</v>
+        <v>1355.7</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>7600</v>
+        <v>8000</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>16.3</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>124.2</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1300</v>
+        <v>1230</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>40.1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>16.3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>2</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.2</v>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>8.6</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="16">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>1.1</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>17.8</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>71.3</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3050</v>
+        <v>3100</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>5.8</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>29</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1750</v>
+        <v>1900</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>25.1</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>43.9</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1250</v>
+        <v>1280</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>15.9</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>57.3</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2800</v>
+        <v>2850</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>7.6</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>21.2</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="29">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1550</v>
+        <v>1480</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>12</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>18.6</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>3.6</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1670</v>
+        <v>1680</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>530</v>
+        <v>610</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>650</v>
+        <v>580</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>36.9</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="39">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>780</v>
+        <v>880</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>18.2</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="41">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1450</v>
+        <v>1580</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>74</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>107.3</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1450</v>
+        <v>1430</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>15.9</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>155</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>59.7</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="46">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>5</v>
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>56.8</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>76.59999999999999</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="49">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2450</v>
+        <v>2620</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>9.5</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>23.2</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="52">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>920</v>
+        <v>960</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1570</v>
+        <v>1770</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>9.5</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>14.9</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="56">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>40.3</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>18.5</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>880</v>
+        <v>970</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>20.1</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>17.7</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="59">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>850</v>
+        <v>700</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>9.5</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>3200</v>
+        <v>3050</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>1.3</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2450</v>
+        <v>2000</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>37.7</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>92.3</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>40.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>20.4</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>15</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1241</v>
+        <v>1212</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>37.5</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1700</v>
+        <v>1820</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>18.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>32</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="67">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>750</v>
+        <v>835</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>10.1</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="71">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>892.8</v>
+        <v>920.5</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>309.5</v>
+        <v>315.9</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>137</v>
+        <v>119.3</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1339.2</v>
+        <v>1355.7</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7505.9</v>
+        <v>7522.4</v>
       </c>
     </row>
     <row r="9">
@@ -2777,19 +2777,19 @@
       </c>
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="7" t="n">
-        <v>4814.3</v>
+        <v>4842.1</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1596.9</v>
+        <v>1603.3</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1094.7</v>
+        <v>1077</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>7505.9</v>
+        <v>7522.4</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>7505.9</v>
+        <v>7522.4</v>
       </c>
     </row>
   </sheetData>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.06.08.pdf</t>
+          <t>Revenue Meeting_2026.06.16.pdf</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.06.08</t>
+          <t>2026.06.16</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>920.5</v>
+        <v>892.8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>315.9</v>
+        <v>309.5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>119.3</v>
+        <v>137</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1355.7</v>
+        <v>1339.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7522.4</v>
+        <v>7505.9</v>
       </c>
     </row>
     <row r="9">
@@ -2777,19 +2777,19 @@
       </c>
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="7" t="n">
-        <v>4842.1</v>
+        <v>4814.3</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1603.3</v>
+        <v>1596.9</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1077</v>
+        <v>1094.7</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>7522.4</v>
+        <v>7505.9</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>7522.4</v>
+        <v>7505.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>892.8</v>
+        <v>920.5</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>309.5</v>
+        <v>315.9</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>137</v>
+        <v>119.3</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1339.2</v>
+        <v>1355.7</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7505.9</v>
+        <v>7522.4</v>
       </c>
     </row>
     <row r="9">
@@ -2777,19 +2777,19 @@
       </c>
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="7" t="n">
-        <v>4814.3</v>
+        <v>4842.1</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1596.9</v>
+        <v>1603.3</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1094.7</v>
+        <v>1077</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>7505.9</v>
+        <v>7522.4</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>7505.9</v>
+        <v>7522.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>892.8</v>
+        <v>920.5</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>309.5</v>
+        <v>315.9</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>137</v>
+        <v>119.3</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1339.2</v>
+        <v>1355.7</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7505.9</v>
+        <v>7522.4</v>
       </c>
     </row>
     <row r="9">
@@ -2777,19 +2777,19 @@
       </c>
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="7" t="n">
-        <v>4814.3</v>
+        <v>4842.1</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1596.9</v>
+        <v>1603.3</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1094.7</v>
+        <v>1077</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>7505.9</v>
+        <v>7522.4</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>7505.9</v>
+        <v>7522.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -477,7 +477,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 예상매출 - 2026-06  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
+          <t>소사업 예상매출 - 2026-07  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
         </is>
       </c>
     </row>
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9295</v>
+        <v>11850</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>130.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>135.9</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>764</v>
+        <v>2910</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>8.5</v>
+        <v>16.6</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>9.1</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>830</v>
+        <v>1620</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1800</v>
+        <v>3550</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>830</v>
+        <v>1400</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="8">
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>670</v>
+        <v>720</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0.3</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7014</v>
+        <v>8164</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>69.5</v>
+        <v>59</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>17.8</v>
+        <v>20.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>87.7</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3180</v>
+        <v>3900</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>47.6</v>
+        <v>46.8</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>60.7</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6763</v>
+        <v>5910</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>21.6</v>
+        <v>56.5</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>84.90000000000001</v>
+        <v>118.7</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4269</v>
+        <v>5413</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>81.7</v>
+        <v>102.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>17.8</v>
+        <v>30.5</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>100.2</v>
+        <v>134.3</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2742</v>
+        <v>2750</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>32.3</v>
+        <v>31.2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>36.6</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1206</v>
+        <v>1600</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.4</v>
+        <v>8.1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2710</v>
+        <v>4109</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>80.3</v>
+        <v>120.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>20.6</v>
+        <v>31.5</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>100.8</v>
+        <v>152.7</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3010</v>
+        <v>3800</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>116.9</v>
+        <v>137.5</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>22.8</v>
+        <v>29.7</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>139.6</v>
+        <v>167.3</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1222</v>
+        <v>1338</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>55.8</v>
+        <v>79.2</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>84</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>140.4</v>
+        <v>146.1</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2802</v>
+        <v>3800</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>79.5</v>
+        <v>67</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>19.4</v>
+        <v>39.5</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>99</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4642</v>
+        <v>5570</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>24.8</v>
+        <v>34.6</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>13.9</v>
+        <v>18.8</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>38.7</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2824</v>
+        <v>3695</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>8.9</v>
+        <v>12.2</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>16.8</v>
+        <v>13.1</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>25.9</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1490</v>
+        <v>1380</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>20.1</v>
+        <v>15.5</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>19.5</v>
+        <v>9</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>39.8</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5750</v>
+        <v>6500</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>75.3</v>
+        <v>111.9</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>85.8</v>
+        <v>126.5</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3032</v>
+        <v>2400</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>21.2</v>
+        <v>52.9</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>19.5</v>
+        <v>31.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>36.6</v>
+        <v>22.7</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>77.40000000000001</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3570</v>
+        <v>3800</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>34.2</v>
+        <v>4</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>7.7</v>
+        <v>22.3</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>41.9</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1285</v>
+        <v>1230</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>11.3</v>
+        <v>7.8</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>15.9</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>71700</v>
+        <v>87409</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>920.5</v>
+        <v>957.3</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>315.9</v>
+        <v>420</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>119.3</v>
+        <v>142.7</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1355.7</v>
+        <v>1520</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1063,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 세그먼트별 - 2026-06</t>
+          <t>소사업 세그먼트별 - 2026-07</t>
         </is>
       </c>
     </row>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>130.8</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1230</v>
+        <v>2700</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>520</v>
+        <v>2050</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.5</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>240</v>
+        <v>860</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>450</v>
+        <v>800</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>380</v>
+        <v>820</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1100</v>
+        <v>2100</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>700</v>
+        <v>1450</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>25.5</v>
+        <v>468.4</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0</v>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>530</v>
+        <v>800</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="17">
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>25.5</v>
+        <v>468.4</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0.3</v>
@@ -1466,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>29.3</v>
+        <v>10.8</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3900</v>
+        <v>4350</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>17.8</v>
+        <v>13.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>69.5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3100</v>
+        <v>3800</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>17.8</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="23">
@@ -1529,10 +1529,10 @@
         <v>14</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>29</v>
+        <v>38.2</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1900</v>
+        <v>2400</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>25.1</v>
+        <v>19.5</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>47.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1280</v>
+        <v>1500</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>10.2</v>
+        <v>9.1</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3900</v>
+        <v>3250</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>15.9</v>
+        <v>19.1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2850</v>
+        <v>2660</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>7.6</v>
+        <v>21.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>21.6</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="29">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>94.2</v>
+        <v>54.5</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2600</v>
+        <v>3350</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>31.4</v>
+        <v>30.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>81.7</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1480</v>
+        <v>1950</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>17.8</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1680</v>
+        <v>1620</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>32.3</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1050</v>
+        <v>1130</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>610</v>
+        <v>950</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>5.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>580</v>
+        <v>650</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>36.9</v>
+        <v>38.8</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1830</v>
+        <v>2750</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>80.3</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>880</v>
+        <v>1350</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>20.6</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="41">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1580</v>
+        <v>2150</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>116.9</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1430</v>
+        <v>1650</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>15.9</v>
+        <v>18</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>22.8</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>155</v>
+        <v>176.1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>55.8</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>750</v>
+        <v>850</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>112</v>
+        <v>78.3</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>84</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>56.8</v>
+        <v>31.9</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>79.5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>13.9</v>
+        <v>23.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>19.4</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="50">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D50" s="4" t="n">
         <v>35.9</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2620</v>
+        <v>3020</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>24.8</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2020</v>
+        <v>2550</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>13.9</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="53">
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D53" s="4" t="n">
         <v>0</v>
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>960</v>
+        <v>1345</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>8.9</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1770</v>
+        <v>2350</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>9.5</v>
+        <v>5.6</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>16.8</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="56">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>2.4</v>
+        <v>23.8</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>40.3</v>
+        <v>25.9</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>20.1</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>970</v>
+        <v>780</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>20.1</v>
+        <v>11.6</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>19.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>6.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>3050</v>
+        <v>2600</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>37.7</v>
+        <v>37.3</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>75.3</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>520</v>
+        <v>650</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>40.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>21.2</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>15</v>
+        <v>31.3</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>19.5</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1212</v>
+        <v>750</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>36.6</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1820</v>
+        <v>2200</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>34.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1750</v>
+        <v>1600</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>7.7</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>835</v>
+        <v>580</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>11.3</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="71">
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2566,7 +2566,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 월별 누적 - 2026-06 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
+          <t>소사업 월별 누적 - 2026-07 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
         </is>
       </c>
     </row>
@@ -2770,26 +2770,53 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RM FCST</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>957.3</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>142.7</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1520</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>9042.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="7" t="n">
-        <v>4842.1</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>1603.3</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>1077</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>7522.4</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>7522.4</v>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="7" t="n">
+        <v>5799.4</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2023.3</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1219.7</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>9042.4</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>9042.4</v>
       </c>
     </row>
   </sheetData>
@@ -2818,7 +2845,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2857,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전년 2025-06 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-07 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>812.2</v>
+        <v>814.9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>182</v>
+        <v>183.1</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>157.7</v>
+        <v>163.7</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1151.9</v>
+        <v>1161.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6166.7</v>
+        <v>6176.3</v>
       </c>
     </row>
     <row r="8">
@@ -2766,7 +2766,7 @@
         <v>1355.7</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7522.4</v>
+        <v>7532.1</v>
       </c>
     </row>
     <row r="9">
@@ -2793,7 +2793,7 @@
         <v>1520</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9042.4</v>
+        <v>9052.1</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5799.4</v>
+        <v>5802.1</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2023.3</v>
+        <v>2024.4</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1219.7</v>
+        <v>1225.6</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9042.4</v>
+        <v>9052.1</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9042.4</v>
+        <v>9052.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>11850</v>
+        <v>11650</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>72.90000000000001</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2910</v>
+        <v>2460</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>16.6</v>
+        <v>13.4</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>19.3</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1620</v>
+        <v>1570</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>6.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3550</v>
+        <v>3520</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -611,16 +611,16 @@
         <v>1400</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>8164</v>
+        <v>8655</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>59</v>
+        <v>65.8</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>79.7</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3900</v>
+        <v>3950</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>46.8</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13.7</v>
+        <v>14.2</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>60.5</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5910</v>
+        <v>6150</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>62.2</v>
+        <v>65</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>56.5</v>
+        <v>58.5</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>118.7</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5413</v>
+        <v>5644</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>102.7</v>
+        <v>107.3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>30.5</v>
+        <v>31.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>134.3</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2750</v>
+        <v>2625</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>35.1</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1600</v>
+        <v>1733</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>3.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>11.5</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>4109</v>
+        <v>4220</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>120.6</v>
+        <v>122.8</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>31.5</v>
+        <v>32.7</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>152.7</v>
+        <v>156.7</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3800</v>
+        <v>3720</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>137.5</v>
+        <v>143.9</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>29.7</v>
+        <v>26.5</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>167.3</v>
+        <v>170.4</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1338</v>
+        <v>1354</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>79.2</v>
+        <v>88</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>146.1</v>
+        <v>151.2</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>3800</v>
+        <v>3855</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>67</v>
+        <v>63.9</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>39.5</v>
+        <v>43</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>106.5</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5570</v>
+        <v>5550</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>34.6</v>
+        <v>36</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>18.8</v>
+        <v>17.7</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>53.4</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3695</v>
+        <v>3600</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>25.4</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6500</v>
+        <v>6700</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>111.9</v>
+        <v>115.6</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>126.5</v>
+        <v>130.4</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2400</v>
+        <v>2609</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>52.9</v>
+        <v>42.3</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>31.3</v>
+        <v>34.4</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>22.7</v>
+        <v>29.9</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>106.9</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="24">
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>22.3</v>
@@ -994,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>26.3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1230</v>
+        <v>1330</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>14.5</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>87409</v>
+        <v>88055</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>957.3</v>
+        <v>973.5</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>420</v>
+        <v>422.1</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>142.7</v>
+        <v>155.7</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1520</v>
+        <v>1551.4</v>
       </c>
     </row>
   </sheetData>
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2050</v>
+        <v>1650</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>16.6</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>860</v>
+        <v>810</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>820</v>
+        <v>770</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1450</v>
+        <v>1420</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>13.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>59</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3800</v>
+        <v>3785</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>5.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>38.2</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>13.7</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3250</v>
+        <v>3400</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>19.1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>62.2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2660</v>
+        <v>2750</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>21.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>56.5</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3350</v>
+        <v>3500</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>30.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>102.7</v>
+        <v>107.3</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>30.5</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1620</v>
+        <v>1600</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1130</v>
+        <v>1025</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>950</v>
+        <v>1065</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="37">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>38.8</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>120.6</v>
+        <v>122.8</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>31.5</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="41">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="42">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2150</v>
+        <v>2250</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>64</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>137.5</v>
+        <v>143.9</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1650</v>
+        <v>1470</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>18</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>29.7</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>176.1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>79.2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>78.3</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2100</v>
+        <v>2005</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>67</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1700</v>
+        <v>1850</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>23.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>39.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3020</v>
+        <v>3150</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>34.6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2550</v>
+        <v>2400</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>7.4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>18.8</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="53">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1345</v>
+        <v>1300</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2350</v>
+        <v>2300</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="56">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>600</v>
+        <v>560</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>25.9</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>780</v>
+        <v>850</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>11.6</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>37.3</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>111.9</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>650</v>
+        <v>520</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>52.9</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>31.3</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>750</v>
+        <v>989</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>22.7</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="67">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>580</v>
+        <v>640</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>650</v>
+        <v>690</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>920.5</v>
+        <v>974.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>315.9</v>
+        <v>319.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>119.3</v>
+        <v>106.6</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1355.7</v>
+        <v>1400.1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7532.1</v>
+        <v>7576.5</v>
       </c>
     </row>
     <row r="9">
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>957.3</v>
+        <v>973.5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>420</v>
+        <v>422.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>142.7</v>
+        <v>155.7</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1520</v>
+        <v>1551.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9052.1</v>
+        <v>9127.799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5802.1</v>
+        <v>5872</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2024.4</v>
+        <v>2029.9</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1225.6</v>
+        <v>1225.9</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9052.1</v>
+        <v>9127.799999999999</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9052.1</v>
+        <v>9127.799999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.06.16.pdf</t>
+          <t>Revenue Meeting_2026.06.23.pdf</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.06.16</t>
+          <t>2026.06.23</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -2619,19 +2619,19 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>836.4</v>
+        <v>1.6</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>287.3</v>
+        <v>1.1</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>139.3</v>
+        <v>2.2</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1263</v>
+        <v>4.8</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1263</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="4">
@@ -2646,19 +2646,19 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1102.3</v>
+        <v>0</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>400.6</v>
+        <v>0</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>214.3</v>
+        <v>1.2</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1717.3</v>
+        <v>1.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2980.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5">
@@ -2673,19 +2673,19 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>430.5</v>
+        <v>0</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>193.3</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>184.5</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>808.3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>3788.5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="6">
@@ -2700,19 +2700,19 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>740.2</v>
+        <v>0</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>224.1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>261.9</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1226.2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5014.7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="7">
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>814.9</v>
+        <v>812.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>183.1</v>
+        <v>182</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>163.7</v>
+        <v>157.7</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1161.6</v>
+        <v>1151.9</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6176.3</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="8">
@@ -2766,7 +2766,7 @@
         <v>1400.1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7576.5</v>
+        <v>2558.1</v>
       </c>
     </row>
     <row r="9">
@@ -2793,7 +2793,7 @@
         <v>1551.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9127.799999999999</v>
+        <v>4109.5</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5872</v>
+        <v>2761.5</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2029.9</v>
+        <v>924.5</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1225.9</v>
+        <v>423.4</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9127.799999999999</v>
+        <v>4109.5</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9127.799999999999</v>
+        <v>4109.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2619,19 +2619,19 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1.6</v>
+        <v>836.4</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1.1</v>
+        <v>287.3</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2.2</v>
+        <v>139.3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>4.8</v>
+        <v>1263</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>4.8</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="4">
@@ -2646,19 +2646,19 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>1102.3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0</v>
+        <v>400.6</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1.2</v>
+        <v>214.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.2</v>
+        <v>1717.3</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>6.1</v>
+        <v>2980.3</v>
       </c>
     </row>
     <row r="5">
@@ -2673,19 +2673,19 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>430.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0</v>
+        <v>193.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0</v>
+        <v>184.5</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0</v>
+        <v>808.3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>6.1</v>
+        <v>3788.5</v>
       </c>
     </row>
     <row r="6">
@@ -2700,19 +2700,19 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>740.2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0</v>
+        <v>224.1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>261.9</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>1226.2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.1</v>
+        <v>5014.7</v>
       </c>
     </row>
     <row r="7">
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>812.2</v>
+        <v>814.9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>182</v>
+        <v>183.1</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>157.7</v>
+        <v>163.7</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1151.9</v>
+        <v>1161.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1158</v>
+        <v>6176.3</v>
       </c>
     </row>
     <row r="8">
@@ -2766,7 +2766,7 @@
         <v>1400.1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2558.1</v>
+        <v>7576.5</v>
       </c>
     </row>
     <row r="9">
@@ -2793,7 +2793,7 @@
         <v>1551.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4109.5</v>
+        <v>9127.799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>2761.5</v>
+        <v>5872</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>924.5</v>
+        <v>2029.9</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>423.4</v>
+        <v>1225.9</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>4109.5</v>
+        <v>9127.799999999999</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>4109.5</v>
+        <v>9127.799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2750,23 +2750,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RM FCST</t>
+          <t>온북</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>974.2</v>
+        <v>990.7</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>319.3</v>
+        <v>319.4</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>106.6</v>
+        <v>104.7</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1400.1</v>
+        <v>1414.8</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7576.5</v>
+        <v>7591.1</v>
       </c>
     </row>
     <row r="9">
@@ -2793,7 +2793,7 @@
         <v>1551.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9127.799999999999</v>
+        <v>9142.5</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5872</v>
+        <v>5888.4</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2029.9</v>
+        <v>2030</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1225.9</v>
+        <v>1224.1</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9127.799999999999</v>
+        <v>9142.5</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9127.799999999999</v>
+        <v>9142.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2750,23 +2750,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>온북</t>
+          <t>RM FCST</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>990.7</v>
+        <v>974.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>319.4</v>
+        <v>319.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>104.7</v>
+        <v>106.6</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1414.8</v>
+        <v>1400.1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7591.1</v>
+        <v>7576.5</v>
       </c>
     </row>
     <row r="9">
@@ -2793,7 +2793,7 @@
         <v>1551.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9142.5</v>
+        <v>9127.799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5888.4</v>
+        <v>5872</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2030</v>
+        <v>2029.9</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1224.1</v>
+        <v>1225.9</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9142.5</v>
+        <v>9127.799999999999</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9142.5</v>
+        <v>9127.799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -520,10 +520,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>11650</v>
+        <v>12150</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>72.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>8</v>
@@ -532,7 +532,7 @@
         <v>5.6</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>86.5</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="4">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3520</v>
+        <v>3450</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -608,13 +608,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1400</v>
+        <v>1380</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>8655</v>
+        <v>8734</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>65.8</v>
+        <v>66.5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>86.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6150</v>
+        <v>6250</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>65</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>58.5</v>
@@ -708,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>123.5</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5644</v>
+        <v>5586</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>107.3</v>
+        <v>105.8</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>140</v>
+        <v>138.3</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2625</v>
+        <v>2650</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>30.8</v>
+        <v>33.7</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>34.4</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1733</v>
+        <v>1688</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="15">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>4220</v>
+        <v>4320</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>122.8</v>
+        <v>127.2</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>32.7</v>
@@ -796,7 +796,7 @@
         <v>1.2</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>156.7</v>
+        <v>161.1</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3720</v>
+        <v>3750</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>143.9</v>
+        <v>153.5</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>26.5</v>
+        <v>24.3</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>170.4</v>
+        <v>177.9</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1354</v>
+        <v>1414</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>88</v>
+        <v>96.8</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>62.7</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>151.2</v>
+        <v>160.1</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>3855</v>
+        <v>3750</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>63.9</v>
+        <v>62.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>43</v>
+        <v>41.8</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>106.9</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5550</v>
+        <v>5570</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>36</v>
+        <v>35.7</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3600</v>
+        <v>3563</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>12.9</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="21">
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1410</v>
+        <v>1400</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>9.800000000000001</v>
@@ -928,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6700</v>
+        <v>7250</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>5.1</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>115.6</v>
+        <v>138</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>130.4</v>
+        <v>152.2</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2609</v>
+        <v>2706</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>42.3</v>
+        <v>46.4</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>34.4</v>
+        <v>36</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>106.7</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3600</v>
+        <v>3650</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>26</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1330</v>
+        <v>1430</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>15.7</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>88055</v>
+        <v>89411</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>973.5</v>
+        <v>1007.5</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>422.1</v>
+        <v>418.7</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>155.7</v>
+        <v>178.8</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1551.4</v>
+        <v>1605</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>72.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1420</v>
+        <v>1200</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="20">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4850</v>
+        <v>4900</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>13.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>65.8</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3785</v>
+        <v>3800</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>5.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>38.2</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="24">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>19.1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>65</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3500</v>
+        <v>3450</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>30.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>107.3</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="31">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1600</v>
+        <v>1750</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>30.8</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1025</v>
+        <v>900</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1065</v>
+        <v>1050</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>650</v>
+        <v>620</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="38">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>122.8</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="40">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2250</v>
+        <v>2400</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>64</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>143.9</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1470</v>
+        <v>1350</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>18</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>26.5</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>176.1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>88</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="46">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2005</v>
+        <v>1950</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>63.9</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1850</v>
+        <v>1800</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>23.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>43</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3150</v>
+        <v>3120</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>36</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>7.4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="53">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="55">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D56" s="4" t="n">
         <v>23.8</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="57">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>25.9</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="58">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="61">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3100</v>
+        <v>3700</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>37.3</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>115.6</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>520</v>
+        <v>570</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>42.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>34.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1600</v>
+        <v>1550</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>14</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>640</v>
+        <v>770</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>690</v>
+        <v>660</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="71">
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>973.5</v>
+        <v>1007.5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>422.1</v>
+        <v>418.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>155.7</v>
+        <v>178.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1551.4</v>
+        <v>1605</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9142.5</v>
+        <v>9196.1</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5888.4</v>
+        <v>5922.3</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2030</v>
+        <v>2026.6</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1224.1</v>
+        <v>1247.2</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9142.5</v>
+        <v>9196.1</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9142.5</v>
+        <v>9196.1</v>
       </c>
     </row>
   </sheetData>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.06.23.pdf</t>
+          <t>Revenue Meeting_2026.06.30.pdf</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.06.23</t>
+          <t>2026.06.30</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,7 +477,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 예상매출 - 2026-07  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
+          <t>소사업 예상매출 - 2026-06  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
         </is>
       </c>
     </row>
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>12150</v>
+        <v>9568</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>76.90000000000001</v>
+        <v>134.9</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>90.5</v>
+        <v>140.1</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2460</v>
+        <v>729</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>13.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>15.9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1570</v>
+        <v>800</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6">
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3450</v>
+        <v>1790</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1380</v>
+        <v>760</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="8">
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>740</v>
+        <v>670</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0.3</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>8734</v>
+        <v>7164</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>66.5</v>
+        <v>71.3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3950</v>
+        <v>3300</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>46.8</v>
+        <v>49.4</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>14.2</v>
+        <v>13.6</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>60.9</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6250</v>
+        <v>7013</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>58.5</v>
+        <v>21.2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>125.4</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5586</v>
+        <v>4474</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>105.8</v>
+        <v>88</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>31.3</v>
+        <v>18</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>138.3</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2650</v>
+        <v>2772</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>33.7</v>
+        <v>33.3</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>36.8</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1688</v>
+        <v>1321</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.9</v>
+        <v>6.2</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12.9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>4320</v>
+        <v>2825</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>127.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>32.7</v>
+        <v>21.6</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>161.1</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3750</v>
+        <v>3190</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>153.5</v>
+        <v>133.1</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>24.3</v>
+        <v>22.1</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>177.9</v>
+        <v>155.3</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1414</v>
+        <v>1268</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>96.8</v>
+        <v>62</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>62.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>160.1</v>
+        <v>147.7</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>3750</v>
+        <v>2852</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>62.2</v>
+        <v>82.3</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>41.8</v>
+        <v>19.4</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>104</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5570</v>
+        <v>4772</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>35.7</v>
+        <v>26.3</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>18.1</v>
+        <v>13.7</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>53.8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3563</v>
+        <v>2884</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11.4</v>
+        <v>8.9</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>12.9</v>
+        <v>17.4</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>24.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1400</v>
+        <v>1510</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>14.2</v>
+        <v>20.1</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>24.1</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>7250</v>
+        <v>5150</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.1</v>
+        <v>6.6</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>138</v>
+        <v>64</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>152.2</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2706</v>
+        <v>3075</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>46.4</v>
+        <v>22.5</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>36</v>
+        <v>20.4</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>29.8</v>
+        <v>35.2</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>112.2</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3650</v>
+        <v>3679</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.8</v>
+        <v>36.4</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>21.6</v>
+        <v>7.7</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>25.4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1430</v>
+        <v>1320</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>17.1</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>89411</v>
+        <v>72886</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1007.5</v>
+        <v>974.2</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>418.7</v>
+        <v>319.3</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>178.8</v>
+        <v>106.6</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1605</v>
+        <v>1400.1</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1063,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 세그먼트별 - 2026-07</t>
+          <t>소사업 세그먼트별 - 2026-06</t>
         </is>
       </c>
     </row>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9500</v>
+        <v>8250</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>8.1</v>
+        <v>16.3</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>76.90000000000001</v>
+        <v>134.9</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2500</v>
+        <v>1250</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>37.5</v>
+        <v>40.1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1650</v>
+        <v>505</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.1</v>
+        <v>16.3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>810</v>
+        <v>220</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>37.5</v>
+        <v>40.1</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>800</v>
+        <v>440</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.1</v>
+        <v>16.3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>770</v>
+        <v>360</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>37.5</v>
+        <v>40.1</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2250</v>
+        <v>1120</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1200</v>
+        <v>670</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>468.4</v>
+        <v>25.5</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0</v>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>930</v>
+        <v>480</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>450</v>
+        <v>280</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>468.4</v>
+        <v>25.5</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="19">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0.3</v>
@@ -1466,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>10.8</v>
+        <v>29.3</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4900</v>
+        <v>4000</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>13.6</v>
+        <v>17.8</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>66.5</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3800</v>
+        <v>3150</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>38.2</v>
+        <v>29</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2400</v>
+        <v>1970</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>19.5</v>
+        <v>25.1</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>46.8</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1550</v>
+        <v>1330</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>9.1</v>
+        <v>10.2</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>14.2</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="26">
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3500</v>
+        <v>4200</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>19.1</v>
+        <v>15.9</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>66.90000000000001</v>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>21.3</v>
+        <v>7.6</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>58.5</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="29">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>54.5</v>
+        <v>94.2</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="30">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3450</v>
+        <v>2800</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>30.7</v>
+        <v>31.4</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>105.8</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>15.6</v>
+        <v>12</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>31.3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1750</v>
+        <v>1730</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>33.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>900</v>
+        <v>1030</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="35">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="36">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1050</v>
+        <v>705</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>8.9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="D37" s="4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>5.2</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>3.2</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>38.8</v>
+        <v>36.9</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2900</v>
+        <v>1900</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>127.2</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1400</v>
+        <v>925</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>32.7</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="41">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>153.5</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1350</v>
+        <v>1390</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>18</v>
+        <v>15.9</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>24.3</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>176.1</v>
+        <v>155</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>96.8</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>800</v>
+        <v>760</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>78.3</v>
+        <v>112</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>62.7</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1950</v>
+        <v>1450</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>31.9</v>
+        <v>56.8</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>62.2</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1800</v>
+        <v>1400</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>23.2</v>
+        <v>13.9</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>41.8</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="50">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D50" s="4" t="n">
         <v>35.9</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="51">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3120</v>
+        <v>2780</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>11.4</v>
+        <v>9.5</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>35.7</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2450</v>
+        <v>1990</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>18.1</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="53">
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D53" s="4" t="n">
         <v>0</v>
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1250</v>
+        <v>960</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>11.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2300</v>
+        <v>1830</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>5.6</v>
+        <v>9.5</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>12.9</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="56">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>23.8</v>
+        <v>2.4</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="57">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>25.9</v>
+        <v>40.3</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>14.2</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>850</v>
+        <v>990</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>11.6</v>
+        <v>20.1</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="59">
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="60">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>850</v>
+        <v>700</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>10.7</v>
+        <v>9.5</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>9.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3700</v>
+        <v>1700</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>138</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>81.40000000000001</v>
+        <v>40.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>46.4</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1150</v>
+        <v>1360</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>31.3</v>
+        <v>15</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>36</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>986</v>
+        <v>1165</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>29.8</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2100</v>
+        <v>1934</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>1.8</v>
+        <v>18.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>3.8</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1550</v>
+        <v>1745</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>14</v>
+        <v>4.4</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>21.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>770</v>
+        <v>885</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>10.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>660</v>
+        <v>435</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="71">
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2566,7 +2566,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 월별 누적 - 2026-07 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
+          <t>소사업 월별 누적 - 2026-06 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
         </is>
       </c>
     </row>
@@ -2750,73 +2750,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>온북</t>
+          <t>RM FCST</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>990.7</v>
+        <v>974.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>319.4</v>
+        <v>319.3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>104.7</v>
+        <v>106.6</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1414.8</v>
+        <v>1400.1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7591.1</v>
+        <v>7576.5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7월</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>RM FCST</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1007.5</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>418.7</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>178.8</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>1605</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>9196.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="7" t="n">
-        <v>5922.3</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>2026.6</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>1247.2</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>9196.1</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>9196.1</v>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="7" t="n">
+        <v>4898.4</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1607.8</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>1070.3</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>7576.5</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>7576.5</v>
       </c>
     </row>
   </sheetData>
@@ -2845,7 +2818,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2830,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전년 2025-07 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-06 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -477,7 +477,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 예상매출 - 2026-06  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
+          <t>소사업 예상매출 - 2026-07  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
         </is>
       </c>
     </row>
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9568</v>
+        <v>12150</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>134.9</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>140.1</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>729</v>
+        <v>2460</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>8.9</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>800</v>
+        <v>1570</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6">
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1790</v>
+        <v>3450</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>760</v>
+        <v>1380</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>670</v>
+        <v>740</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0.3</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7164</v>
+        <v>8734</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>71.3</v>
+        <v>66.5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>89.8</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3300</v>
+        <v>3950</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>49.4</v>
+        <v>46.8</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>63</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7013</v>
+        <v>6250</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>21.2</v>
+        <v>58.5</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>89.3</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4474</v>
+        <v>5586</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>88</v>
+        <v>105.8</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>18</v>
+        <v>31.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>106.7</v>
+        <v>138.3</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2772</v>
+        <v>2650</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>37.5</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1321</v>
+        <v>1688</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>6.2</v>
+        <v>8.9</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2825</v>
+        <v>4320</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>127.2</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>21.6</v>
+        <v>32.7</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>105</v>
+        <v>161.1</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3190</v>
+        <v>3750</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>133.1</v>
+        <v>153.5</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>155.3</v>
+        <v>177.9</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1268</v>
+        <v>1414</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>62</v>
+        <v>96.8</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>85.09999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>147.7</v>
+        <v>160.1</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2852</v>
+        <v>3750</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>82.3</v>
+        <v>62.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>19.4</v>
+        <v>41.8</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>101.8</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4772</v>
+        <v>5570</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>26.3</v>
+        <v>35.7</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>13.7</v>
+        <v>18.1</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>40</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2884</v>
+        <v>3563</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>8.9</v>
+        <v>11.4</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>17.4</v>
+        <v>12.9</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>26.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1510</v>
+        <v>1400</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>20.1</v>
+        <v>14.2</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>19.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>40.2</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5150</v>
+        <v>7250</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6.6</v>
+        <v>9.1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>74.09999999999999</v>
+        <v>152.2</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3075</v>
+        <v>2706</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>22.5</v>
+        <v>46.4</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>20.4</v>
+        <v>36</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>35.2</v>
+        <v>29.8</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>78.09999999999999</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3679</v>
+        <v>3650</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>36.4</v>
+        <v>3.8</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>7.7</v>
+        <v>21.6</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>44</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1320</v>
+        <v>1430</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>16.4</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>72886</v>
+        <v>89411</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>974.2</v>
+        <v>1007.5</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>319.3</v>
+        <v>418.7</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>106.6</v>
+        <v>178.8</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1400.1</v>
+        <v>1605</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1063,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 세그먼트별 - 2026-06</t>
+          <t>소사업 세그먼트별 - 2026-07</t>
         </is>
       </c>
     </row>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>8250</v>
+        <v>9500</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>134.9</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1250</v>
+        <v>2500</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>505</v>
+        <v>1650</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>220</v>
+        <v>810</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>440</v>
+        <v>800</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>360</v>
+        <v>770</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1120</v>
+        <v>2250</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>670</v>
+        <v>1200</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>25.5</v>
+        <v>468.4</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0</v>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>480</v>
+        <v>930</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>280</v>
+        <v>450</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>25.5</v>
+        <v>468.4</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0.3</v>
@@ -1466,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>29.3</v>
+        <v>10.8</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4000</v>
+        <v>4900</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>17.8</v>
+        <v>13.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>71.3</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3150</v>
+        <v>3800</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>29</v>
+        <v>38.2</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="24">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1970</v>
+        <v>2400</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>25.1</v>
+        <v>19.5</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>49.4</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1330</v>
+        <v>1550</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>10.2</v>
+        <v>9.1</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="26">
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4200</v>
+        <v>3500</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>15.9</v>
+        <v>19.1</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>66.90000000000001</v>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2800</v>
+        <v>2750</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>7.6</v>
+        <v>21.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>21.2</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="29">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>94.2</v>
+        <v>54.5</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2800</v>
+        <v>3450</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>31.4</v>
+        <v>30.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>88</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>18</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1730</v>
+        <v>1750</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1030</v>
+        <v>900</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="35">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>705</v>
+        <v>1050</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>6.2</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>36.9</v>
+        <v>38.8</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1900</v>
+        <v>2900</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>925</v>
+        <v>1400</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>21.6</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="41">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="42">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>133.1</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1390</v>
+        <v>1350</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>15.9</v>
+        <v>18</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>155</v>
+        <v>176.1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>62</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>112</v>
+        <v>78.3</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>85.09999999999999</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1450</v>
+        <v>1950</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>56.8</v>
+        <v>31.9</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>82.3</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>13.9</v>
+        <v>23.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>19.4</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="50">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D50" s="4" t="n">
         <v>35.9</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2780</v>
+        <v>3120</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>26.3</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1990</v>
+        <v>2450</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>13.7</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="53">
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D53" s="4" t="n">
         <v>0</v>
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>960</v>
+        <v>1250</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>8.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1830</v>
+        <v>2300</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>9.5</v>
+        <v>5.6</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>17.4</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="56">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>2.4</v>
+        <v>23.8</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="57">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>40.3</v>
+        <v>25.9</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>20.1</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>990</v>
+        <v>850</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>20.1</v>
+        <v>11.6</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>19.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>700</v>
+        <v>850</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>6.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1700</v>
+        <v>3700</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>37.7</v>
+        <v>37.3</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>64</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>40.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>22.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1360</v>
+        <v>1150</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>15</v>
+        <v>31.3</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>20.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1165</v>
+        <v>986</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>35.2</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1934</v>
+        <v>2100</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>36.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1745</v>
+        <v>1550</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>7.7</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>885</v>
+        <v>770</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>435</v>
+        <v>660</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="71">
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2566,7 +2566,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 월별 누적 - 2026-06 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
+          <t>소사업 월별 누적 - 2026-07 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
         </is>
       </c>
     </row>
@@ -2750,46 +2750,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>온북</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>990.7</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>319.4</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>1414.8</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>7591.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>RM FCST</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>974.2</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>319.3</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>106.6</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>1400.1</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>7576.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="n">
+        <v>1007.5</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1605</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>9196.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="7" t="n">
-        <v>4898.4</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>1607.8</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>1070.3</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>7576.5</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>7576.5</v>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="7" t="n">
+        <v>5922.3</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2026.6</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1247.2</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>9196.1</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>9196.1</v>
       </c>
     </row>
   </sheetData>
@@ -2818,7 +2845,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2857,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전년 2025-06 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-07 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,7 +477,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 예상매출 - 2026-06  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
+          <t>소사업 예상매출 - 2026-07  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
         </is>
       </c>
     </row>
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9568</v>
+        <v>12150</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>134.9</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>140.1</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>729</v>
+        <v>2460</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>8.9</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>800</v>
+        <v>1570</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6">
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1790</v>
+        <v>3450</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>760</v>
+        <v>1380</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>670</v>
+        <v>740</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0.3</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7164</v>
+        <v>8734</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>71.3</v>
+        <v>66.5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>89.8</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3300</v>
+        <v>3950</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>49.4</v>
+        <v>46.8</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>63</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7013</v>
+        <v>6250</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>21.2</v>
+        <v>58.5</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>89.3</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4474</v>
+        <v>5586</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>88</v>
+        <v>105.8</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>18</v>
+        <v>31.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>106.7</v>
+        <v>138.3</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2772</v>
+        <v>2650</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>37.5</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1321</v>
+        <v>1688</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>6.2</v>
+        <v>8.9</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2825</v>
+        <v>4320</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>127.2</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>21.6</v>
+        <v>32.7</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>105</v>
+        <v>161.1</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3190</v>
+        <v>3750</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>133.1</v>
+        <v>153.5</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>155.3</v>
+        <v>177.9</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1268</v>
+        <v>1414</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>62</v>
+        <v>96.8</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>85.09999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>147.7</v>
+        <v>160.1</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2852</v>
+        <v>3750</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>82.3</v>
+        <v>62.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>19.4</v>
+        <v>41.8</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>101.8</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4772</v>
+        <v>5570</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>26.3</v>
+        <v>35.7</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>13.7</v>
+        <v>18.1</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>40</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2884</v>
+        <v>3563</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>8.9</v>
+        <v>11.4</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>17.4</v>
+        <v>12.9</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>26.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1510</v>
+        <v>1400</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>20.1</v>
+        <v>14.2</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>19.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>40.2</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5150</v>
+        <v>7250</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6.6</v>
+        <v>9.1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>74.09999999999999</v>
+        <v>152.2</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3075</v>
+        <v>2706</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>22.5</v>
+        <v>46.4</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>20.4</v>
+        <v>36</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>35.2</v>
+        <v>29.8</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>78.09999999999999</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3679</v>
+        <v>3650</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>36.4</v>
+        <v>3.8</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>7.7</v>
+        <v>21.6</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>44</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1320</v>
+        <v>1430</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>16.4</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>72886</v>
+        <v>89411</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>974.2</v>
+        <v>1007.5</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>319.3</v>
+        <v>418.7</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>106.6</v>
+        <v>178.8</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1400.1</v>
+        <v>1605</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1063,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 세그먼트별 - 2026-06</t>
+          <t>소사업 세그먼트별 - 2026-07</t>
         </is>
       </c>
     </row>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>8250</v>
+        <v>9500</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>134.9</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1250</v>
+        <v>2500</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>505</v>
+        <v>1650</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>220</v>
+        <v>810</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>440</v>
+        <v>800</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16.3</v>
+        <v>8.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>360</v>
+        <v>770</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>40.1</v>
+        <v>37.5</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1120</v>
+        <v>2250</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>670</v>
+        <v>1200</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>25.5</v>
+        <v>468.4</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0</v>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>480</v>
+        <v>930</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>280</v>
+        <v>450</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>25.5</v>
+        <v>468.4</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.4</v>
+        <v>1.8</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0.3</v>
@@ -1466,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>29.3</v>
+        <v>10.8</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4000</v>
+        <v>4900</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>17.8</v>
+        <v>13.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>71.3</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3150</v>
+        <v>3800</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>29</v>
+        <v>38.2</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="24">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1970</v>
+        <v>2400</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>25.1</v>
+        <v>19.5</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>49.4</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1330</v>
+        <v>1550</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>10.2</v>
+        <v>9.1</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="26">
@@ -1610,10 +1610,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4200</v>
+        <v>3500</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>15.9</v>
+        <v>19.1</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>66.90000000000001</v>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2800</v>
+        <v>2750</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>7.6</v>
+        <v>21.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>21.2</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="29">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>94.2</v>
+        <v>54.5</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2800</v>
+        <v>3450</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>31.4</v>
+        <v>30.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>88</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>18</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1730</v>
+        <v>1750</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1030</v>
+        <v>900</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="35">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>705</v>
+        <v>1050</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>6.2</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>36.9</v>
+        <v>38.8</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1900</v>
+        <v>2900</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>925</v>
+        <v>1400</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>21.6</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="41">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="42">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>133.1</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1390</v>
+        <v>1350</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>15.9</v>
+        <v>18</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>155</v>
+        <v>176.1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>62</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>112</v>
+        <v>78.3</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>85.09999999999999</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1450</v>
+        <v>1950</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>56.8</v>
+        <v>31.9</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>82.3</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>13.9</v>
+        <v>23.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>19.4</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="50">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D50" s="4" t="n">
         <v>35.9</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2780</v>
+        <v>3120</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>26.3</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1990</v>
+        <v>2450</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>13.7</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="53">
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D53" s="4" t="n">
         <v>0</v>
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>960</v>
+        <v>1250</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>8.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1830</v>
+        <v>2300</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>9.5</v>
+        <v>5.6</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>17.4</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="56">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>2.4</v>
+        <v>23.8</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="57">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>40.3</v>
+        <v>25.9</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>20.1</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>990</v>
+        <v>850</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>20.1</v>
+        <v>11.6</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>19.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>700</v>
+        <v>850</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>6.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1700</v>
+        <v>3700</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>37.7</v>
+        <v>37.3</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>64</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>40.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>22.5</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1360</v>
+        <v>1150</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>15</v>
+        <v>31.3</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>20.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1165</v>
+        <v>986</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>35.2</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1934</v>
+        <v>2100</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>36.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1745</v>
+        <v>1550</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>7.7</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>885</v>
+        <v>770</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>435</v>
+        <v>660</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="71">
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2566,7 +2566,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 월별 누적 - 2026-06 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
+          <t>소사업 월별 누적 - 2026-07 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
         </is>
       </c>
     </row>
@@ -2750,46 +2750,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>온북</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>990.7</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>319.4</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>1414.8</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>7591.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>RM FCST</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>974.2</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>319.3</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>106.6</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>1400.1</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>7576.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="n">
+        <v>1007.5</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1605</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>9196.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="7" t="n">
-        <v>4898.4</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>1607.8</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>1070.3</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>7576.5</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>7576.5</v>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="7" t="n">
+        <v>5922.3</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2026.6</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1247.2</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>9196.1</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>9196.1</v>
       </c>
     </row>
   </sheetData>
@@ -2818,7 +2845,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2857,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전년 2025-06 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-07 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>12150</v>
+        <v>12100</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>76.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>90.5</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1570</v>
+        <v>1350</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>6.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3450</v>
+        <v>3350</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>7.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1380</v>
+        <v>1270</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>8734</v>
+        <v>8933</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>66.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>20.1</v>
+        <v>18</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>1.3</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3950</v>
+        <v>4050</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>46.8</v>
+        <v>49.7</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>60.9</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6250</v>
+        <v>6300</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>58.5</v>
+        <v>50</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>125.4</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5586</v>
+        <v>5110</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>105.8</v>
+        <v>101.2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>31.3</v>
+        <v>26.1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>138.3</v>
+        <v>128.6</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2650</v>
+        <v>3240</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>33.7</v>
+        <v>40.6</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>36.8</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1688</v>
+        <v>1748</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12.9</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="15">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>4320</v>
+        <v>4370</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>127.2</v>
+        <v>129.4</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>32.7</v>
@@ -796,7 +796,7 @@
         <v>1.2</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>161.1</v>
+        <v>163.3</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3750</v>
+        <v>3980</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>153.5</v>
+        <v>163.1</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>24.3</v>
+        <v>25.8</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>177.9</v>
+        <v>188.9</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1414</v>
+        <v>1360</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>96.8</v>
+        <v>88</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>62.7</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>160.1</v>
+        <v>151.2</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>3750</v>
+        <v>3700</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>62.2</v>
+        <v>70.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>41.8</v>
+        <v>34.9</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5570</v>
+        <v>5600</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>35.7</v>
+        <v>37.2</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>53.8</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3563</v>
+        <v>3413</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>24.5</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>14.2</v>
+        <v>12.9</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>24.1</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>7250</v>
+        <v>7190</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>138</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>152.2</v>
+        <v>152.1</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2706</v>
+        <v>2814</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>46.4</v>
+        <v>40.7</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>36</v>
+        <v>34.4</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>29.8</v>
+        <v>36.7</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>112.2</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="24">
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3650</v>
+        <v>3890</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>21.6</v>
@@ -994,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1430</v>
+        <v>1460</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>89411</v>
+        <v>89728</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1007.5</v>
+        <v>1035.9</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>418.7</v>
+        <v>393.1</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>178.8</v>
+        <v>183.8</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1605</v>
+        <v>1612.9</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>76.90000000000001</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>37.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>770</v>
+        <v>550</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>930</v>
+        <v>850</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4900</v>
+        <v>5500</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>13.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>66.5</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3800</v>
+        <v>3400</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>5.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>20.1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>38.2</v>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2400</v>
+        <v>2550</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>19.5</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>46.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3500</v>
+        <v>3950</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>19.1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2750</v>
+        <v>2350</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>21.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>58.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3450</v>
+        <v>3300</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>30.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>105.8</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2000</v>
+        <v>1670</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>31.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1750</v>
+        <v>2110</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>33.7</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>900</v>
+        <v>1130</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="38">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2900</v>
+        <v>2950</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>127.2</v>
+        <v>129.4</v>
       </c>
     </row>
     <row r="40">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2400</v>
+        <v>2550</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>64</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>153.5</v>
+        <v>163.1</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1350</v>
+        <v>1430</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>18</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>24.3</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>176.1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>96.8</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1950</v>
+        <v>2200</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>62.2</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>23.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>41.8</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3120</v>
+        <v>3250</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>35.7</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2450</v>
+        <v>2350</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>7.4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="53">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1250</v>
+        <v>1150</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="56">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>25.9</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>14.2</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>11.6</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2700</v>
+        <v>2640</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>570</v>
+        <v>500</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>46.4</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>36</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>986</v>
+        <v>1214</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>29.8</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2100</v>
+        <v>2340</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="67">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>770</v>
+        <v>810</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="71">
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1007.5</v>
+        <v>1035.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>418.7</v>
+        <v>393.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>178.8</v>
+        <v>183.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1605</v>
+        <v>1612.9</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9196.1</v>
+        <v>9204</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5922.3</v>
+        <v>5950.8</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2026.6</v>
+        <v>2001</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1247.2</v>
+        <v>1252.2</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9196.1</v>
+        <v>9204</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9196.1</v>
+        <v>9204</v>
       </c>
     </row>
   </sheetData>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.06.30.pdf</t>
+          <t>Revenue Meeting_2026.07.07.pdf</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.06.30</t>
+          <t>2026.07.07</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1035.9</v>
+        <v>1007.5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>393.1</v>
+        <v>418.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>183.8</v>
+        <v>178.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1612.9</v>
+        <v>1605</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9204</v>
+        <v>9196.1</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5950.8</v>
+        <v>5922.3</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2001</v>
+        <v>2026.6</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1252.2</v>
+        <v>1247.2</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9204</v>
+        <v>9196.1</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9204</v>
+        <v>9196.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1007.5</v>
+        <v>1035.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>418.7</v>
+        <v>393.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>178.8</v>
+        <v>183.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1605</v>
+        <v>1612.9</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9196.1</v>
+        <v>9204</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5922.3</v>
+        <v>5950.8</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2026.6</v>
+        <v>2001</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1247.2</v>
+        <v>1252.2</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9196.1</v>
+        <v>9204</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9196.1</v>
+        <v>9204</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>12100</v>
+        <v>12580</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>77.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>89.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2460</v>
+        <v>2257</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>13.4</v>
+        <v>12.4</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1350</v>
+        <v>1280</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3350</v>
+        <v>3200</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1270</v>
+        <v>1350</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="8">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>740</v>
+        <v>690</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.7</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>8933</v>
+        <v>8729</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>18</v>
+        <v>17.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>93.90000000000001</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="10">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6300</v>
+        <v>6350</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>75.5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>125.5</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5110</v>
+        <v>4738</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>101.2</v>
+        <v>93.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>26.1</v>
+        <v>24.2</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>128.6</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3240</v>
+        <v>3450</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>40.6</v>
+        <v>44.2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>44.6</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="14">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1748</v>
+        <v>1827</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>3.3</v>
@@ -774,7 +774,7 @@
         <v>0.7</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>13.3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>4370</v>
+        <v>4320</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>129.4</v>
+        <v>127.2</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>32.7</v>
@@ -796,7 +796,7 @@
         <v>1.2</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>163.3</v>
+        <v>161.1</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3980</v>
+        <v>4050</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>163.1</v>
+        <v>169.5</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>188.9</v>
+        <v>194.8</v>
       </c>
     </row>
     <row r="17">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1360</v>
+        <v>1290</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>88</v>
+        <v>75.7</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>62.7</v>
@@ -840,7 +840,7 @@
         <v>0.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>151.2</v>
+        <v>138.9</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>3700</v>
+        <v>3850</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>70.2</v>
+        <v>71.8</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>34.9</v>
+        <v>37.2</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>105</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5600</v>
+        <v>5150</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>37.2</v>
+        <v>35.7</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>17.3</v>
+        <v>15</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>54.5</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3413</v>
+        <v>3263</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>10.5</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>23.4</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="21">
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1300</v>
+        <v>1320</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>9.199999999999999</v>
@@ -928,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>7190</v>
+        <v>7200</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>138</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>152.1</v>
+        <v>152.6</v>
       </c>
     </row>
     <row r="23">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2814</v>
+        <v>2791</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>40.7</v>
@@ -969,10 +969,10 @@
         <v>34.4</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>36.7</v>
+        <v>36</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>111.8</v>
+        <v>111.1</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3890</v>
+        <v>4120</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>21.6</v>
+        <v>23</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>25.9</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1460</v>
+        <v>1445</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>89728</v>
+        <v>89300</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1035.9</v>
+        <v>1029.1</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>393.1</v>
+        <v>390.3</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>183.8</v>
+        <v>182.4</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1612.9</v>
+        <v>1601.8</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9600</v>
+        <v>10200</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>77.7</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>37.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1650</v>
+        <v>1530</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.4</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>810</v>
+        <v>720</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>37.5</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>1.8</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>1</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5500</v>
+        <v>5450</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>13.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3400</v>
+        <v>3250</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>5.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>18</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>38.2</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="24">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>21.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3300</v>
+        <v>3050</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>30.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>101.2</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1670</v>
+        <v>1550</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>26.1</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2110</v>
+        <v>2300</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>40.6</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1130</v>
+        <v>1150</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1100</v>
+        <v>1180</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>38.8</v>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2950</v>
+        <v>2900</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>129.4</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="40">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2550</v>
+        <v>2650</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>64</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>163.1</v>
+        <v>169.5</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1430</v>
+        <v>1400</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>18</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>176.1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>88</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="46">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>70.2</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>23.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>34.9</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3250</v>
+        <v>3120</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>37.2</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2350</v>
+        <v>2030</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>7.4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>17.3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2250</v>
+        <v>2100</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="56">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>25.9</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="58">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2640</v>
+        <v>2600</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="62">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1214</v>
+        <v>1191</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>36.7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2340</v>
+        <v>2470</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1550</v>
+        <v>1650</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>14</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>21.6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>650</v>
+        <v>620</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="71">
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1035.9</v>
+        <v>1029.1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>393.1</v>
+        <v>390.3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>183.8</v>
+        <v>182.4</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1612.9</v>
+        <v>1601.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9204</v>
+        <v>9192.9</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5950.8</v>
+        <v>5944</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2001</v>
+        <v>1998.2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1252.2</v>
+        <v>1250.8</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9204</v>
+        <v>9192.9</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9204</v>
+        <v>9192.9</v>
       </c>
     </row>
   </sheetData>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.07.07.pdf</t>
+          <t>Revenue Meeting_2026.07.14.pdf</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.07.07</t>
+          <t>2026.07.14</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1029.1</v>
+        <v>1035.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>390.3</v>
+        <v>393.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>182.4</v>
+        <v>183.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1601.8</v>
+        <v>1612.9</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9192.9</v>
+        <v>9204</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5944</v>
+        <v>5950.8</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1998.2</v>
+        <v>2001</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1250.8</v>
+        <v>1252.2</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9192.9</v>
+        <v>9204</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9192.9</v>
+        <v>9204</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1035.9</v>
+        <v>1029.1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>393.1</v>
+        <v>390.3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>183.8</v>
+        <v>182.4</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1612.9</v>
+        <v>1601.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9204</v>
+        <v>9192.9</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5950.8</v>
+        <v>5944</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2001</v>
+        <v>1998.2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1252.2</v>
+        <v>1250.8</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9204</v>
+        <v>9192.9</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9204</v>
+        <v>9192.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>12580</v>
+        <v>12293</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>92.90000000000001</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2257</v>
+        <v>1997</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="5">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1280</v>
+        <v>1215</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>1.6</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3200</v>
+        <v>2900</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1350</v>
+        <v>1200</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.7</v>
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>8729</v>
+        <v>8879</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>73.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>17.2</v>
+        <v>17.7</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>1.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>92.2</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4050</v>
+        <v>3989</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>49.7</v>
+        <v>48.2</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>63.4</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="11">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6350</v>
+        <v>6400</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>75.5</v>
+        <v>76.5</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>51</v>
@@ -708,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>126.6</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4738</v>
+        <v>4338</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>93.5</v>
+        <v>85.8</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>24.2</v>
+        <v>21.9</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>1.3</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>119.1</v>
+        <v>109.1</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3450</v>
+        <v>3550</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>44.2</v>
+        <v>45.2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>48.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1827</v>
+        <v>1690</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>14</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>4320</v>
+        <v>4414</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>127.2</v>
+        <v>134.2</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>32.7</v>
+        <v>31.2</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>161.1</v>
+        <v>166.6</v>
       </c>
     </row>
     <row r="16">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>4050</v>
+        <v>4070</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>169.5</v>
+        <v>170.8</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>25.2</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>194.8</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1290</v>
+        <v>1190</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>75.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>62.7</v>
+        <v>58.7</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>138.9</v>
+        <v>126.2</v>
       </c>
     </row>
     <row r="18">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5150</v>
+        <v>4730</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>35.7</v>
+        <v>32</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>50.7</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3263</v>
+        <v>3163</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>22.5</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1320</v>
+        <v>1130</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>13.5</v>
+        <v>11.7</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>22.7</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>7200</v>
+        <v>7150</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>138</v>
+        <v>137.3</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>152.6</v>
+        <v>152.4</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2791</v>
+        <v>2671</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>40.7</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>34.4</v>
+        <v>31.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>111.1</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>4120</v>
+        <v>4050</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>23</v>
+        <v>24.4</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>27.5</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1445</v>
+        <v>1385</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>17.5</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>89300</v>
+        <v>86924</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1029.1</v>
+        <v>1011.9</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>390.3</v>
+        <v>377.4</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>182.4</v>
+        <v>180.9</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1601.8</v>
+        <v>1570.2</v>
       </c>
     </row>
   </sheetData>
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2300</v>
+        <v>2020</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>37.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1530</v>
+        <v>1400</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>720</v>
+        <v>590</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="8">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>780</v>
+        <v>715</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="10">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>900</v>
+        <v>820</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17">
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>1.8</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>1</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5450</v>
+        <v>5500</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>13.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>73.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3250</v>
+        <v>3350</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>5.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>17.2</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="23">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2550</v>
+        <v>2475</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>19.5</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>49.7</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1500</v>
+        <v>1514</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3950</v>
+        <v>4000</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>19.1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>75.5</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="28">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3050</v>
+        <v>2800</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>30.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>93.5</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1550</v>
+        <v>1400</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>24.2</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="32">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2300</v>
+        <v>2350</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>44.2</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1180</v>
+        <v>1090</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>630</v>
+        <v>580</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>38.8</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2900</v>
+        <v>3060</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>127.2</v>
+        <v>134.2</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1400</v>
+        <v>1334</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>32.7</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="41">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2650</v>
+        <v>2670</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>64</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>169.5</v>
+        <v>170.8</v>
       </c>
     </row>
     <row r="43">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>176.1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>75.7</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>78.3</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>62.7</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="47">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3120</v>
+        <v>2800</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>35.7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2030</v>
+        <v>1930</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>7.4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>15</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="53">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1150</v>
+        <v>1000</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2100</v>
+        <v>2150</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>25.9</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>13.5</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>800</v>
+        <v>680</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>11.6</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="59">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>900</v>
+        <v>970</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3700</v>
+        <v>3680</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>37.3</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>138</v>
+        <v>137.3</v>
       </c>
     </row>
     <row r="63">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>34.4</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1191</v>
+        <v>1171</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>36</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2470</v>
+        <v>2300</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1650</v>
+        <v>1750</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>14</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>23</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>825</v>
+        <v>790</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>620</v>
+        <v>595</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="71">
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1029.1</v>
+        <v>1011.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>390.3</v>
+        <v>377.4</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>182.4</v>
+        <v>180.9</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1601.8</v>
+        <v>1570.2</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9192.9</v>
+        <v>9161.299999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5944</v>
+        <v>5926.8</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1998.2</v>
+        <v>1985.3</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1250.8</v>
+        <v>1249.3</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9192.9</v>
+        <v>9161.299999999999</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9192.9</v>
+        <v>9161.299999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.07.14.pdf</t>
+          <t>Revenue Meeting_2026.07.21.pdf</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.07.14</t>
+          <t>2026.07.21</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1011.9</v>
+        <v>1029.1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>377.4</v>
+        <v>390.3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>180.9</v>
+        <v>182.4</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1570.2</v>
+        <v>1601.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9161.299999999999</v>
+        <v>9192.9</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5926.8</v>
+        <v>5944</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1985.3</v>
+        <v>1998.2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1249.3</v>
+        <v>1250.8</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9161.299999999999</v>
+        <v>9192.9</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9161.299999999999</v>
+        <v>9192.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1029.1</v>
+        <v>1011.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>390.3</v>
+        <v>377.4</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>182.4</v>
+        <v>180.9</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1601.8</v>
+        <v>1570.2</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9192.9</v>
+        <v>9161.299999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5944</v>
+        <v>5926.8</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1998.2</v>
+        <v>1985.3</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1250.8</v>
+        <v>1249.3</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9192.9</v>
+        <v>9161.299999999999</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9192.9</v>
+        <v>9161.299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>12293</v>
+        <v>12185</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>82.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>91.8</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1997</v>
+        <v>2017</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1215</v>
+        <v>1155</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2900</v>
+        <v>2720</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1200</v>
+        <v>1170</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2.7</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>670</v>
+        <v>560</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>8879</v>
+        <v>8459</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>17.7</v>
+        <v>16.8</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>1.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3989</v>
+        <v>3884</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>48.2</v>
+        <v>47.5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>62.1</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6400</v>
+        <v>6246</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>76.5</v>
+        <v>74.3</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>51</v>
+        <v>50.2</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>127.5</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4338</v>
+        <v>4201</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>85.8</v>
+        <v>85.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>21.9</v>
+        <v>19.9</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>1.3</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>109.1</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3550</v>
+        <v>3565</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>49.4</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1690</v>
+        <v>1596</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0.8</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>4414</v>
+        <v>4331</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>134.2</v>
+        <v>133.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>31.2</v>
+        <v>29.6</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>166.6</v>
+        <v>164.4</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>4070</v>
+        <v>3970</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>170.8</v>
+        <v>169.3</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>25.2</v>
+        <v>23.8</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>196</v>
+        <v>193.2</v>
       </c>
     </row>
     <row r="17">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1190</v>
+        <v>1140</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>58.1</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>58.7</v>
@@ -840,7 +840,7 @@
         <v>0.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>126.2</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>3850</v>
+        <v>3782</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>71.8</v>
+        <v>71.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>37.2</v>
+        <v>36</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>108.9</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4730</v>
+        <v>4624</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>32</v>
+        <v>31.6</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>46.3</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3163</v>
+        <v>3200</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1130</v>
+        <v>1150</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>11.7</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>7150</v>
+        <v>6934</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>137.3</v>
+        <v>138.3</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>152.4</v>
+        <v>151.9</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2671</v>
+        <v>2598</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>40.7</v>
+        <v>38.7</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>31.3</v>
+        <v>29.7</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>107.4</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>4050</v>
+        <v>3988</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>4.2</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1385</v>
+        <v>1362</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>86924</v>
+        <v>84837</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1011.9</v>
+        <v>989.3</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>377.4</v>
+        <v>365</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>180.9</v>
+        <v>182.1</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1570.2</v>
+        <v>1536.4</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10200</v>
+        <v>10110</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>82.59999999999999</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2020</v>
+        <v>2000</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>37.5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>715</v>
+        <v>690</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>500</v>
+        <v>465</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>3.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>900</v>
+        <v>820</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="14">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>820</v>
+        <v>795</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>3.3</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>1.9</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>300</v>
+        <v>230</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5500</v>
+        <v>5255</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>13.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3350</v>
+        <v>3175</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>5.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>17.7</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="23">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2475</v>
+        <v>2436</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>19.5</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>48.2</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1514</v>
+        <v>1448</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4000</v>
+        <v>3886</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>19.1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>76.5</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2400</v>
+        <v>2360</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>21.3</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>51</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2800</v>
+        <v>2788</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>30.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>85.8</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1400</v>
+        <v>1275</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>21.9</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="32">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2350</v>
+        <v>2395</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1200</v>
+        <v>1170</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1090</v>
+        <v>1050</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>580</v>
+        <v>526</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="38">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3060</v>
+        <v>3045</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>134.2</v>
+        <v>133.6</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1334</v>
+        <v>1266</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>31.2</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="41">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2670</v>
+        <v>2647</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>64</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>170.8</v>
+        <v>169.3</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1400</v>
+        <v>1323</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>18</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>25.2</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>176.1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="46">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2250</v>
+        <v>2232</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>71.8</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1600</v>
+        <v>1550</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>23.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>37.2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2800</v>
+        <v>2760</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>32</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1930</v>
+        <v>1864</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>7.4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="53">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>9.1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2150</v>
+        <v>2180</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>5.6</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="56">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>11.6</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="59">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>970</v>
+        <v>845</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>10.7</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2500</v>
+        <v>2380</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>1.9</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3680</v>
+        <v>3709</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>37.3</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>137.3</v>
+        <v>138.3</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>40.7</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>31.3</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>31.3</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="66">
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2300</v>
+        <v>2314</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.8</v>
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1750</v>
+        <v>1674</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>14</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>24.4</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>790</v>
+        <v>775</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.07.21.pdf</t>
+          <t>Revenue Meeting_2026.07.28.pdf</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.07.21</t>
+          <t>2026.07.28</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1011.9</v>
+        <v>989.3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>377.4</v>
+        <v>365</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>180.9</v>
+        <v>182.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1570.2</v>
+        <v>1536.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9161.299999999999</v>
+        <v>9127.6</v>
       </c>
     </row>
     <row r="10">
@@ -2804,19 +2804,19 @@
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="7" t="n">
-        <v>5926.8</v>
+        <v>5904.2</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1985.3</v>
+        <v>1972.9</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1249.3</v>
+        <v>1250.5</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9161.299999999999</v>
+        <v>9127.6</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9161.299999999999</v>
+        <v>9127.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,7 +477,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 예상매출 - 2026-07  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
+          <t>소사업 예상매출 - 2026-08  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
         </is>
       </c>
     </row>
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>12185</v>
+        <v>15080</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>81.8</v>
+        <v>100.1</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>91.09999999999999</v>
+        <v>119.2</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2017</v>
+        <v>3100</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>11.7</v>
+        <v>18.3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>13.8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1155</v>
+        <v>1650</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>7.1</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2720</v>
+        <v>3550</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.3</v>
+        <v>11</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.9</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1170</v>
+        <v>1600</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>560</v>
+        <v>840</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0.2</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>8459</v>
+        <v>10318</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>71.3</v>
+        <v>76.2</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>16.8</v>
+        <v>30.9</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>89.2</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3884</v>
+        <v>3650</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>47.5</v>
+        <v>20</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>60.7</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6246</v>
+        <v>5000</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>74.3</v>
+        <v>52.2</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>50.2</v>
+        <v>54.3</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>124.5</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4201</v>
+        <v>7957</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>85.5</v>
+        <v>155.1</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>19.9</v>
+        <v>44.8</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>106.7</v>
+        <v>200.8</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3565</v>
+        <v>3700</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>46.1</v>
+        <v>44.2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>50.2</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1596</v>
+        <v>2018</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>12.4</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>4331</v>
+        <v>5320</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>133.6</v>
+        <v>153.5</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>29.6</v>
+        <v>42.5</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>164.4</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3970</v>
+        <v>4200</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>169.3</v>
+        <v>168.8</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>23.8</v>
+        <v>38.5</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>193.2</v>
+        <v>207.3</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1140</v>
+        <v>1633</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>58.1</v>
+        <v>43.8</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>58.7</v>
+        <v>25.4</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>117.4</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>3782</v>
+        <v>4650</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>71.2</v>
+        <v>37.7</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>36</v>
+        <v>25.6</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>107.2</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4624</v>
+        <v>5630</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>31.6</v>
+        <v>36.3</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>13.7</v>
+        <v>26.7</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>45.3</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3200</v>
+        <v>3067</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>12.2</v>
+        <v>4.7</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>21.7</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1150</v>
+        <v>1380</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>11.7</v>
+        <v>14.8</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>8.1</v>
+        <v>14.8</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>19.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6934</v>
+        <v>6950</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.1</v>
+        <v>21.4</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>138.3</v>
+        <v>112.2</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>151.9</v>
+        <v>136.7</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2598</v>
+        <v>3306</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>38.7</v>
+        <v>22.3</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>29.7</v>
+        <v>12.1</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>103.9</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3988</v>
+        <v>3950</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>23.4</v>
+        <v>20.2</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>27.6</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1362</v>
+        <v>1369</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>10.5</v>
+        <v>11.9</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>16.5</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>84837</v>
+        <v>99918</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>989.3</v>
+        <v>1023.5</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>365</v>
+        <v>399.2</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>182.1</v>
+        <v>156</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1536.4</v>
+        <v>1578.7</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1063,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 세그먼트별 - 2026-07</t>
+          <t>소사업 세그먼트별 - 2026-08</t>
         </is>
       </c>
     </row>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10110</v>
+        <v>12000</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>81.8</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>37.5</v>
+        <v>45.6</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1450</v>
+        <v>2200</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.7</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>560</v>
+        <v>900</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>37.5</v>
+        <v>45.6</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>690</v>
+        <v>1000</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>465</v>
+        <v>650</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>37.5</v>
+        <v>45.6</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1900</v>
+        <v>2300</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>820</v>
+        <v>1250</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>795</v>
+        <v>1100</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="17">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19">
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>230</v>
+        <v>340</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0.2</v>
@@ -1466,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>10.8</v>
+        <v>3.6</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5255</v>
+        <v>6050</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>71.3</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3175</v>
+        <v>4230</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.3</v>
+        <v>7.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>16.8</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>38.2</v>
+        <v>24.8</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2436</v>
+        <v>2050</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>19.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>47.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1448</v>
+        <v>1600</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="26">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>0</v>
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3886</v>
+        <v>3050</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>19.1</v>
+        <v>17.1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>74.3</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2360</v>
+        <v>1950</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>21.3</v>
+        <v>27.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>50.2</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="29">
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>54.5</v>
+        <v>55.9</v>
       </c>
       <c r="E29" s="4" t="n">
         <v>0</v>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2788</v>
+        <v>5100</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>85.5</v>
+        <v>155.1</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1275</v>
+        <v>2820</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>19.9</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2395</v>
+        <v>2300</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>46.1</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1170</v>
+        <v>1400</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>526</v>
+        <v>810</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>38.8</v>
+        <v>42.4</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3045</v>
+        <v>3500</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>133.6</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1266</v>
+        <v>1820</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>29.6</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="41">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2647</v>
+        <v>2700</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>64</v>
+        <v>62.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>169.3</v>
+        <v>168.8</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1323</v>
+        <v>1500</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>18</v>
+        <v>25.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>23.8</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>330</v>
+        <v>550</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>176.1</v>
+        <v>79.7</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>58.1</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>750</v>
+        <v>1050</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>78.3</v>
+        <v>24.2</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>58.7</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>34</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2232</v>
+        <v>2850</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>31.9</v>
+        <v>13.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>71.2</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1550</v>
+        <v>1800</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>23.2</v>
+        <v>14.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>36</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2760</v>
+        <v>3220</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>31.6</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1864</v>
+        <v>2410</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>7.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>13.7</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="53">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1007</v>
+        <v>1200</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>9.1</v>
+        <v>6.8</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2180</v>
+        <v>1850</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>12.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="56">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D56" s="4" t="n">
         <v>23.8</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="57">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>25.9</v>
+        <v>24.7</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>11.7</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>700</v>
+        <v>780</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>11.6</v>
+        <v>18.9</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>8.1</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="59">
@@ -2285,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="E59" s="4" t="n">
         <v>0</v>
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>845</v>
+        <v>1500</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>10.7</v>
+        <v>14.3</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>9.1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2380</v>
+        <v>2600</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3709</v>
+        <v>2850</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>37.3</v>
+        <v>39.4</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>138.3</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>475</v>
+        <v>600</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>81.40000000000001</v>
+        <v>37.1</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>38.7</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>950</v>
+        <v>1500</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>31.3</v>
+        <v>8.1</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>29.7</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1173</v>
+        <v>1206</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2314</v>
+        <v>2450</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1674</v>
+        <v>1500</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>23.4</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>775</v>
+        <v>879</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>10.5</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>587</v>
+        <v>490</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2566,7 +2566,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 월별 누적 - 2026-07 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
+          <t>소사업 월별 누적 - 2026-08 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
         </is>
       </c>
     </row>
@@ -2797,26 +2797,53 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RM FCST</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1023.5</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>399.2</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1578.7</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>10706.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="7" t="n">
-        <v>5904.2</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>1972.9</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>1250.5</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>9127.6</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>9127.6</v>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="7" t="n">
+        <v>6927.7</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2372.1</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>1406.5</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>10706.3</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>10706.3</v>
       </c>
     </row>
   </sheetData>
@@ -2845,7 +2872,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2884,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전년 2025-07 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-08 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2777,23 +2777,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RM FCST</t>
+          <t>온북</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>989.3</v>
+        <v>989.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>365</v>
+        <v>369.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>182.1</v>
+        <v>182.2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1536.4</v>
+        <v>1540.9</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9127.6</v>
+        <v>9132</v>
       </c>
     </row>
     <row r="10">
@@ -2820,7 +2820,7 @@
         <v>1578.7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10706.3</v>
+        <v>10710.7</v>
       </c>
     </row>
     <row r="11">
@@ -2834,16 +2834,16 @@
         <v>6927.7</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2372.1</v>
+        <v>2376.4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1406.5</v>
+        <v>1406.6</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10706.3</v>
+        <v>10710.7</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10706.3</v>
+        <v>10710.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2777,23 +2777,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>온북</t>
+          <t>RM FCST</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>989.4</v>
+        <v>989.3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>369.2</v>
+        <v>365</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>182.2</v>
+        <v>182.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1540.9</v>
+        <v>1536.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9132</v>
+        <v>9127.6</v>
       </c>
     </row>
     <row r="10">
@@ -2820,7 +2820,7 @@
         <v>1578.7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10710.7</v>
+        <v>10706.3</v>
       </c>
     </row>
     <row r="11">
@@ -2834,16 +2834,16 @@
         <v>6927.7</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2376.4</v>
+        <v>2372.1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1406.6</v>
+        <v>1406.5</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10710.7</v>
+        <v>10706.3</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10710.7</v>
+        <v>10706.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -2777,23 +2777,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RM FCST</t>
+          <t>온북</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>989.3</v>
+        <v>989.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>365</v>
+        <v>369.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>182.1</v>
+        <v>182.2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1536.4</v>
+        <v>1540.9</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9127.6</v>
+        <v>9132</v>
       </c>
     </row>
     <row r="10">
@@ -2820,7 +2820,7 @@
         <v>1578.7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10706.3</v>
+        <v>10710.7</v>
       </c>
     </row>
     <row r="11">
@@ -2834,16 +2834,16 @@
         <v>6927.7</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2372.1</v>
+        <v>2376.4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1406.5</v>
+        <v>1406.6</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10706.3</v>
+        <v>10710.7</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10706.3</v>
+        <v>10710.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>990.7</v>
+        <v>991.8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>319.4</v>
+        <v>319.8</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>104.7</v>
+        <v>104.6</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1414.8</v>
+        <v>1416.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7591.1</v>
+        <v>7592.5</v>
       </c>
     </row>
     <row r="9">
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>989.4</v>
+        <v>987.7</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>369.2</v>
+        <v>365.4</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>182.2</v>
+        <v>181.2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1540.9</v>
+        <v>1534.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9132</v>
+        <v>9126.9</v>
       </c>
     </row>
     <row r="10">
@@ -2820,7 +2820,7 @@
         <v>1578.7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10710.7</v>
+        <v>10705.6</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6927.7</v>
+        <v>6927.1</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2376.4</v>
+        <v>2372.9</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1406.6</v>
+        <v>1405.5</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10710.7</v>
+        <v>10705.6</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10710.7</v>
+        <v>10705.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>987.7</v>
+        <v>989.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>365.4</v>
+        <v>369.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>181.2</v>
+        <v>182.2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1534.4</v>
+        <v>1540.9</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9126.9</v>
+        <v>9133.4</v>
       </c>
     </row>
     <row r="10">
@@ -2820,7 +2820,7 @@
         <v>1578.7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10705.6</v>
+        <v>10712.1</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6927.1</v>
+        <v>6928.8</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2372.9</v>
+        <v>2376.7</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1405.5</v>
+        <v>1406.5</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10705.6</v>
+        <v>10712.1</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10705.6</v>
+        <v>10712.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>15080</v>
+        <v>14080</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>100.1</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>15.5</v>
+        <v>14.4</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>3.6</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>119.2</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="4">
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3100</v>
+        <v>3700</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>18.3</v>
+        <v>23.4</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>4.6</v>
@@ -554,7 +554,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1650</v>
+        <v>1550</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>3.4</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>11.7</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3550</v>
+        <v>3520</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1600</v>
+        <v>1780</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="8">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1.6</v>
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10318</v>
+        <v>10331</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>76.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>30.9</v>
+        <v>31.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>108</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="10">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>52.2</v>
+        <v>53.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>54.3</v>
+        <v>55.7</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>106.5</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>7957</v>
+        <v>8101</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>155.1</v>
+        <v>153.6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>44.8</v>
+        <v>47.7</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>200.8</v>
+        <v>202.4</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3700</v>
+        <v>3960</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>44.2</v>
+        <v>46.6</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>49.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2018</v>
+        <v>2098</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5320</v>
+        <v>5653</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>153.5</v>
+        <v>151.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>42.5</v>
+        <v>51.4</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>196</v>
+        <v>202.8</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>168.8</v>
+        <v>165.6</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>38.5</v>
+        <v>37.2</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>207.3</v>
+        <v>202.9</v>
       </c>
     </row>
     <row r="17">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>4650</v>
+        <v>4850</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>63.3</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5630</v>
+        <v>5660</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>26.7</v>
@@ -884,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>63</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3067</v>
+        <v>3097</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1380</v>
+        <v>1650</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>14.8</v>
+        <v>18.5</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>14.8</v>
+        <v>17</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>29.6</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6950</v>
+        <v>6800</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>112.2</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>136.7</v>
+        <v>135.2</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3306</v>
+        <v>3330</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>22.3</v>
+        <v>20.4</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>36.5</v>
+        <v>37.2</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>70.8</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3950</v>
+        <v>4030</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>4.5</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>20.2</v>
+        <v>21.5</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>24.7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1369</v>
+        <v>1380</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>11.9</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>99918</v>
+        <v>100908</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1023.5</v>
+        <v>1019.3</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>399.2</v>
+        <v>416.8</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>156</v>
+        <v>156.9</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1578.7</v>
+        <v>1593</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>12000</v>
+        <v>11200</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>100.1</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>15.5</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="5">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2200</v>
+        <v>2800</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>18.3</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="7">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2300</v>
+        <v>2220</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1100</v>
+        <v>1250</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="17">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0.7</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>6050</v>
+        <v>5950</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>12.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>76.2</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>4230</v>
+        <v>4350</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>7.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>30.9</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>24.8</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3050</v>
+        <v>3100</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>17.1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>52.2</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>27.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>54.3</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>30.4</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>155.1</v>
+        <v>153.6</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2820</v>
+        <v>3000</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>15.9</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>44.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>22.6</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2300</v>
+        <v>2420</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>44.2</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1400</v>
+        <v>1540</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1200</v>
+        <v>1240</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>6.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>810</v>
+        <v>850</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="38">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3500</v>
+        <v>3450</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>153.5</v>
+        <v>151.3</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1820</v>
+        <v>2203</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>42.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="41">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>62.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>168.8</v>
+        <v>165.6</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1500</v>
+        <v>1450</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>25.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>38.5</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="44">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2850</v>
+        <v>3000</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>13.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1800</v>
+        <v>1850</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>14.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3220</v>
+        <v>3250</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>11.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="52">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1850</v>
+        <v>1880</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="56">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>24.7</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>14.8</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>780</v>
+        <v>900</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>18.9</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>14.8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>14.3</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>21.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2600</v>
+        <v>2550</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="62">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>37.1</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>22.3</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1206</v>
+        <v>1230</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>36.5</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="66">
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2450</v>
+        <v>2430</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.8</v>
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>20.2</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="68">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="71">
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1023.5</v>
+        <v>1019.3</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>399.2</v>
+        <v>416.8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>156</v>
+        <v>156.9</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1578.7</v>
+        <v>1593</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10712.1</v>
+        <v>10726.3</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6928.8</v>
+        <v>6924.7</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2376.7</v>
+        <v>2394.2</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1406.5</v>
+        <v>1407.4</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10712.1</v>
+        <v>10726.3</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10712.1</v>
+        <v>10726.3</v>
       </c>
     </row>
   </sheetData>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.07.28.pdf</t>
+          <t>Revenue Meeting_2026.08.04.pdf</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.07.28</t>
+          <t>2026.08.04</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1019.3</v>
+        <v>1023.5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>416.8</v>
+        <v>399.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>156.9</v>
+        <v>156</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1593</v>
+        <v>1578.7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10726.3</v>
+        <v>10712.1</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6924.7</v>
+        <v>6928.8</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2394.2</v>
+        <v>2376.7</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1407.4</v>
+        <v>1406.5</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10726.3</v>
+        <v>10712.1</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10726.3</v>
+        <v>10712.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1023.5</v>
+        <v>1019.3</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>399.2</v>
+        <v>416.8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>156</v>
+        <v>156.9</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1578.7</v>
+        <v>1593</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10712.1</v>
+        <v>10726.3</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6928.8</v>
+        <v>6924.7</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2376.7</v>
+        <v>2394.2</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1406.5</v>
+        <v>1407.4</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10712.1</v>
+        <v>10726.3</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10712.1</v>
+        <v>10726.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>14080</v>
+        <v>13666</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>14.4</v>
+        <v>16</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>111.5</v>
+        <v>106.6</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3700</v>
+        <v>4200</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>23.4</v>
+        <v>27.1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -567,16 +567,16 @@
         <v>1550</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3520</v>
+        <v>3350</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.6</v>
+        <v>9.6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>15.2</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="7">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1780</v>
+        <v>1745</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>1.9</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="8">
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>855</v>
+        <v>800</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0.2</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9">
@@ -655,16 +655,16 @@
         <v>10331</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>31.7</v>
+        <v>32.5</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>107.4</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="10">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>8101</v>
+        <v>8350</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>153.6</v>
+        <v>159.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>47.7</v>
+        <v>48.5</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>202.4</v>
+        <v>209.3</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3960</v>
+        <v>4120</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>46.6</v>
+        <v>49.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>52</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2098</v>
+        <v>2063</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5653</v>
+        <v>5657</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>151.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>202.8</v>
+        <v>202.9</v>
       </c>
     </row>
     <row r="16">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>165.6</v>
+        <v>159.4</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>37.2</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>202.9</v>
+        <v>196.6</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1633</v>
+        <v>1706</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>43.8</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>25.4</v>
+        <v>27.1</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>1.1</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>70.3</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>4850</v>
+        <v>5000</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>39.7</v>
+        <v>40.3</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>26.3</v>
+        <v>27.7</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>66</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5660</v>
+        <v>5130</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>36.6</v>
+        <v>32.7</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>26.7</v>
+        <v>24.7</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>63.3</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3097</v>
+        <v>3197</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1650</v>
+        <v>1860</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>18.5</v>
+        <v>20.2</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>17</v>
+        <v>19.7</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>35.5</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6800</v>
+        <v>6200</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>20</v>
+        <v>17.1</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>2.9</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>112.2</v>
+        <v>98.5</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>135.2</v>
+        <v>118.5</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3330</v>
+        <v>3530</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>20.4</v>
+        <v>19.7</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>12.5</v>
+        <v>13.7</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>37.2</v>
+        <v>39.3</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>70.09999999999999</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>4030</v>
+        <v>4050</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>26</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1380</v>
+        <v>1405</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>100908</v>
+        <v>100660</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1019.3</v>
+        <v>1010.9</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>416.8</v>
+        <v>426.9</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>156.9</v>
+        <v>144.5</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1593</v>
+        <v>1582.4</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>11200</v>
+        <v>10500</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>14.4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>45.6</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2800</v>
+        <v>3250</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>23.4</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="8">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2220</v>
+        <v>2000</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>10.6</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1250</v>
+        <v>1215</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="16">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="19">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0.7</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5950</v>
+        <v>5850</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>12.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>4350</v>
+        <v>4450</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>7.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>31.7</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="23">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5050</v>
+        <v>5250</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>30.4</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>153.6</v>
+        <v>159.7</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>15.9</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>47.7</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>22.6</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2420</v>
+        <v>2550</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>46.6</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1540</v>
+        <v>1570</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1240</v>
+        <v>1150</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>6.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>850</v>
+        <v>905</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="38">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2203</v>
+        <v>2207</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="41">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2650</v>
+        <v>2550</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>62.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>165.6</v>
+        <v>159.4</v>
       </c>
     </row>
     <row r="43">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1050</v>
+        <v>1123</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>24.2</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>25.4</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="47">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>13.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>39.7</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1850</v>
+        <v>1950</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>14.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>26.3</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3250</v>
+        <v>2900</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>11.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>36.6</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2410</v>
+        <v>2230</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>11.1</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>26.7</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="53">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1880</v>
+        <v>1980</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>750</v>
+        <v>820</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>24.7</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>18.5</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>900</v>
+        <v>1040</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>18.9</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>17</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="59">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>14.3</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>20</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="61">
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2550</v>
+        <v>2500</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>1.2</v>
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2850</v>
+        <v>2500</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>39.4</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>112.2</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>37.1</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>20.4</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1550</v>
+        <v>1700</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>12.5</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1230</v>
+        <v>1300</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>37.2</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2430</v>
+        <v>2400</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>880</v>
+        <v>895</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="71">
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1019.3</v>
+        <v>1010.9</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>416.8</v>
+        <v>426.9</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>156.9</v>
+        <v>144.5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1593</v>
+        <v>1582.4</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10726.3</v>
+        <v>10715.7</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6924.7</v>
+        <v>6916.3</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2394.2</v>
+        <v>2404.4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1407.4</v>
+        <v>1395</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10726.3</v>
+        <v>10715.7</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10726.3</v>
+        <v>10715.7</v>
       </c>
     </row>
   </sheetData>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.08.04.pdf</t>
+          <t>Revenue Meeting_2026.08.10.pdf</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.08.04</t>
+          <t>2026.08.10</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1010.9</v>
+        <v>1019.3</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>426.9</v>
+        <v>416.8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>144.5</v>
+        <v>156.9</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1582.4</v>
+        <v>1593</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10715.7</v>
+        <v>10726.3</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6916.3</v>
+        <v>6924.7</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2404.4</v>
+        <v>2394.2</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1395</v>
+        <v>1407.4</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10715.7</v>
+        <v>10726.3</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10715.7</v>
+        <v>10726.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1019.3</v>
+        <v>1010.9</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>416.8</v>
+        <v>426.9</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>156.9</v>
+        <v>144.5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1593</v>
+        <v>1582.4</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10726.3</v>
+        <v>10715.7</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6924.7</v>
+        <v>6916.3</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2394.2</v>
+        <v>2404.4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1407.4</v>
+        <v>1395</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10726.3</v>
+        <v>10715.7</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10726.3</v>
+        <v>10715.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>13666</v>
+        <v>13020</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>87.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>16</v>
+        <v>16.8</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>106.6</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="4">
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>27.1</v>
+        <v>27.9</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>4.9</v>
@@ -554,7 +554,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>32</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1550</v>
+        <v>1560</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="6">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1745</v>
+        <v>1700</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>1.9</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8">
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>800</v>
+        <v>770</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0.2</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10331</v>
+        <v>10281</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>73.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>32.5</v>
+        <v>32.8</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>106.9</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3650</v>
+        <v>3550</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>33.7</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5100</v>
+        <v>4950</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>53.1</v>
+        <v>52.2</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>55.7</v>
+        <v>52.9</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>108.8</v>
+        <v>105.1</v>
       </c>
     </row>
     <row r="12">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>8350</v>
+        <v>8198</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>159.7</v>
+        <v>155.1</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>48.5</v>
@@ -730,7 +730,7 @@
         <v>1.1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>209.3</v>
+        <v>204.7</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>4120</v>
+        <v>4200</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>49.1</v>
+        <v>50</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>54.6</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2063</v>
+        <v>1961</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5657</v>
+        <v>5700</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>151.3</v>
+        <v>157.9</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>51.5</v>
+        <v>49</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>202.9</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1706</v>
+        <v>1619</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>43.8</v>
+        <v>39.8</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>27.1</v>
+        <v>26.2</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>72.09999999999999</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>5000</v>
+        <v>4908</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>40.3</v>
+        <v>39.7</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>27.7</v>
+        <v>27.1</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>68.09999999999999</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5130</v>
+        <v>5160</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>32.7</v>
+        <v>33.1</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>57.4</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3197</v>
+        <v>3167</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="21">
@@ -919,10 +919,10 @@
         <v>1860</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17.1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>98.5</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>118.5</v>
+        <v>118.4</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3530</v>
+        <v>3656</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>19.7</v>
+        <v>20.1</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>39.3</v>
+        <v>40.7</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>72.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>4050</v>
+        <v>3960</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>26.6</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1405</v>
+        <v>1395</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>12.1</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>100660</v>
+        <v>99365</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1010.9</v>
+        <v>999.6</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>426.9</v>
+        <v>422.3</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>144.5</v>
+        <v>146.2</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1582.4</v>
+        <v>1568.1</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10500</v>
+        <v>9700</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>87.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3100</v>
+        <v>3250</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>16</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>45.6</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3250</v>
+        <v>3350</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>27.1</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="7">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>700</v>
+        <v>760</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="11">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1215</v>
+        <v>1170</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="16">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5850</v>
+        <v>5750</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>12.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>73.7</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>4450</v>
+        <v>4500</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>7.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>32.5</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="23">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2050</v>
+        <v>2000</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1600</v>
+        <v>1550</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3100</v>
+        <v>3050</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>17.1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>53.1</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>27.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>55.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5250</v>
+        <v>5100</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>30.4</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>159.7</v>
+        <v>155.1</v>
       </c>
     </row>
     <row r="31">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>22.6</v>
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2550</v>
+        <v>2600</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>49.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1570</v>
+        <v>1600</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1150</v>
+        <v>1080</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>6.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>905</v>
+        <v>870</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>42.4</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3450</v>
+        <v>3600</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>151.3</v>
+        <v>157.9</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2207</v>
+        <v>2100</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>51.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>79.7</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>43.8</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1123</v>
+        <v>1085</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>24.2</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>27.1</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>34</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3050</v>
+        <v>3000</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>13.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>40.3</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1950</v>
+        <v>1908</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>14.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>27.7</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2900</v>
+        <v>2940</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>11.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>32.7</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>11.1</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="53">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>6.8</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1980</v>
+        <v>2000</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="56">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>24.7</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>18.9</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="59">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="62">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>37.1</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>19.7</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1700</v>
+        <v>1770</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1300</v>
+        <v>1346</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>39.3</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2400</v>
+        <v>2260</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="68">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="71">
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1010.9</v>
+        <v>999.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>426.9</v>
+        <v>422.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>144.5</v>
+        <v>146.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1582.4</v>
+        <v>1568.1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10715.7</v>
+        <v>10701.5</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6916.3</v>
+        <v>6905</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2404.4</v>
+        <v>2399.8</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1395</v>
+        <v>1396.7</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10715.7</v>
+        <v>10701.5</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10715.7</v>
+        <v>10701.5</v>
       </c>
     </row>
   </sheetData>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.08.10.pdf</t>
+          <t>Revenue Meeting_2026.08.18.pdf</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.08.10</t>
+          <t>2026.08.18</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>999.6</v>
+        <v>1010.9</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>422.3</v>
+        <v>426.9</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>146.2</v>
+        <v>144.5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1568.1</v>
+        <v>1582.4</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10701.5</v>
+        <v>10715.7</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6905</v>
+        <v>6916.3</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2399.8</v>
+        <v>2404.4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1396.7</v>
+        <v>1395</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10701.5</v>
+        <v>10715.7</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10701.5</v>
+        <v>10715.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1010.9</v>
+        <v>999.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>426.9</v>
+        <v>422.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>144.5</v>
+        <v>146.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1582.4</v>
+        <v>1568.1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10715.7</v>
+        <v>10701.5</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6916.3</v>
+        <v>6905</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2404.4</v>
+        <v>2399.8</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1395</v>
+        <v>1396.7</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10715.7</v>
+        <v>10701.5</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10715.7</v>
+        <v>10701.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>13020</v>
+        <v>12588</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>80.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>100.8</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4300</v>
+        <v>4340</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>27.9</v>
+        <v>28.7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>32.8</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="5">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1560</v>
+        <v>1535</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>3.9</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3350</v>
+        <v>3280</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1700</v>
+        <v>1670</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>1.9</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8">
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>770</v>
+        <v>740</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0.2</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10281</v>
+        <v>10081</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>32.8</v>
+        <v>32.1</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3550</v>
+        <v>3490</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4950</v>
+        <v>4781</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>52.2</v>
+        <v>50.7</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>52.9</v>
+        <v>50.7</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>105.1</v>
+        <v>101.4</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>8198</v>
+        <v>8630</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>155.1</v>
+        <v>163.2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>48.5</v>
+        <v>51.1</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>1.1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>204.7</v>
+        <v>215.4</v>
       </c>
     </row>
     <row r="13">
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>4200</v>
+        <v>4220</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>5.6</v>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>55.7</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1961</v>
+        <v>2011</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>2.6</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5700</v>
+        <v>5660</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>157.9</v>
+        <v>156.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>207</v>
+        <v>205.4</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>4000</v>
+        <v>4017</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>159.4</v>
+        <v>158</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>37.2</v>
+        <v>38.2</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>196.6</v>
+        <v>196.2</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1619</v>
+        <v>1611</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>39.8</v>
+        <v>38.3</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>26.2</v>
+        <v>26.6</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>67.2</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>4908</v>
+        <v>4630</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>39.7</v>
+        <v>38.4</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>27.1</v>
+        <v>24.6</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>66.8</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5160</v>
+        <v>5325</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>33.1</v>
+        <v>34.3</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>24.6</v>
+        <v>25.3</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>57.7</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3167</v>
+        <v>3247</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1860</v>
+        <v>1890</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>19.9</v>
+        <v>20.4</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>39.9</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6100</v>
+        <v>5820</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>17.1</v>
+        <v>15</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>98.5</v>
+        <v>95.3</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>118.4</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3656</v>
+        <v>3665</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>40.7</v>
+        <v>40.1</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3960</v>
+        <v>4020</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>27.1</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1395</v>
+        <v>1405</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>99365</v>
+        <v>98656</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>999.6</v>
+        <v>997.1</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>422.3</v>
+        <v>419.9</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>146.2</v>
+        <v>142.1</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1568.1</v>
+        <v>1559.1</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9700</v>
+        <v>9350</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>80.90000000000001</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3250</v>
+        <v>3170</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>45.6</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3350</v>
+        <v>3440</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>27.9</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>5.2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>5.2</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2000</v>
+        <v>1920</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1350</v>
+        <v>1360</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1170</v>
+        <v>1140</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>4.8</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="16">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5750</v>
+        <v>5650</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>12.6</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>7.3</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>32.8</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="23">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2000</v>
+        <v>1990</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>8.5</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3050</v>
+        <v>2960</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>17.1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>52.2</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1900</v>
+        <v>1821</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>27.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>52.9</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5100</v>
+        <v>5365</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>30.4</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>155.1</v>
+        <v>163.2</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>3050</v>
+        <v>3215</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>15.9</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>48.5</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="32">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>22.6</v>
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2600</v>
+        <v>2620</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="34">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1080</v>
+        <v>1125</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>6.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="37">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>3</v>
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>42.4</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3600</v>
+        <v>3570</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>157.9</v>
+        <v>156.6</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="41">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2550</v>
+        <v>2527</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>62.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>159.4</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1450</v>
+        <v>1490</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>25.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>37.2</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>79.7</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>39.8</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1085</v>
+        <v>1100</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>24.2</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>26.2</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>34</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>13.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>39.7</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1908</v>
+        <v>1730</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>14.2</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>27.1</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2940</v>
+        <v>3045</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>11.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>33.1</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2220</v>
+        <v>2280</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>11.1</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>24.6</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="53">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1150</v>
+        <v>1170</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>6.8</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2000</v>
+        <v>2060</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="56">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>24.7</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>18.9</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>19.9</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="59">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1200</v>
+        <v>1050</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>14.3</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>17.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2500</v>
+        <v>2420</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>39.4</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>98.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>37.1</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1770</v>
+        <v>1790</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>8.1</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1346</v>
+        <v>1325</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>30.2</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>40.7</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2260</v>
+        <v>2380</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.8</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1700</v>
+        <v>1640</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>895</v>
+        <v>925</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="71">
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>999.6</v>
+        <v>997.1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>422.3</v>
+        <v>419.9</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>146.2</v>
+        <v>142.1</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1568.1</v>
+        <v>1559.1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10701.5</v>
+        <v>10692.5</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6905</v>
+        <v>6902.5</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2399.8</v>
+        <v>2397.4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1396.7</v>
+        <v>1392.6</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10701.5</v>
+        <v>10692.5</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10701.5</v>
+        <v>10692.5</v>
       </c>
     </row>
   </sheetData>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.08.18.pdf</t>
+          <t>Revenue Meeting_2026.08.25.pdf</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.08.18</t>
+          <t>2026.08.25</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>997.1</v>
+        <v>999.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>419.9</v>
+        <v>422.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>142.1</v>
+        <v>146.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1559.1</v>
+        <v>1568.1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10692.5</v>
+        <v>10701.5</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6902.5</v>
+        <v>6905</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2397.4</v>
+        <v>2399.8</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1392.6</v>
+        <v>1396.7</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10692.5</v>
+        <v>10701.5</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10692.5</v>
+        <v>10701.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -2808,19 +2808,19 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>999.6</v>
+        <v>997.1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>422.3</v>
+        <v>419.9</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>146.2</v>
+        <v>142.1</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1568.1</v>
+        <v>1559.1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10701.5</v>
+        <v>10692.5</v>
       </c>
     </row>
     <row r="11">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="7" t="n">
-        <v>6905</v>
+        <v>6902.5</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2399.8</v>
+        <v>2397.4</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1396.7</v>
+        <v>1392.6</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10701.5</v>
+        <v>10692.5</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10701.5</v>
+        <v>10692.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -477,7 +477,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 예상매출 - 2026-08  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
+          <t>소사업 예상매출 - 2026-09  (객실 외, GS, VAT제외 / 단위: 백만원)</t>
         </is>
       </c>
     </row>
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>12588</v>
+        <v>5880</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>78</v>
+        <v>60.1</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>16.3</v>
+        <v>12.5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3.1</v>
+        <v>23.7</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>97.40000000000001</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4340</v>
+        <v>1342</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>28.7</v>
+        <v>13.7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>33.3</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1535</v>
+        <v>1100</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6.5</v>
+        <v>9.4</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>10.4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3280</v>
+        <v>1709</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1670</v>
+        <v>1085</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.3</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="8">
@@ -633,16 +633,16 @@
         <v>740</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10081</v>
+        <v>7124</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>100.6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>32.1</v>
+        <v>21.6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>104</v>
+        <v>123.2</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3490</v>
+        <v>2900</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>19.4</v>
+        <v>20.5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>12.8</v>
+        <v>14.8</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>32.2</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="11">
@@ -696,19 +696,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4781</v>
+        <v>5900</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>50.7</v>
+        <v>44.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>50.7</v>
+        <v>19.2</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>101.4</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>8630</v>
+        <v>4490</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>163.2</v>
+        <v>56.4</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>51.1</v>
+        <v>18.1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>215.4</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>4220</v>
+        <v>3352</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>50.4</v>
+        <v>40.4</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>56</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2011</v>
+        <v>1790</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.3</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5660</v>
+        <v>2850</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>156.6</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>48.8</v>
+        <v>22.2</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>205.4</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>4017</v>
+        <v>2416</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>158</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>38.2</v>
+        <v>15.1</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>196.2</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="17">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1611</v>
+        <v>1289</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>38.3</v>
+        <v>24.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>26.6</v>
+        <v>30.4</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>4630</v>
+        <v>2610</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>38.4</v>
+        <v>53.9</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>24.6</v>
+        <v>43.1</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>62.9</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>5325</v>
+        <v>3570</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>34.3</v>
+        <v>16.4</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>25.3</v>
+        <v>12.1</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>59.6</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3247</v>
+        <v>2605</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>7.9</v>
+        <v>5.1</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>13.6</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1890</v>
+        <v>1527</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>20.1</v>
+        <v>12.9</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>20.4</v>
+        <v>15</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>40.5</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5820</v>
+        <v>6850</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>15</v>
+        <v>17.3</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.7</v>
+        <v>6.1</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>95.3</v>
+        <v>110</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>113</v>
+        <v>133.5</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3665</v>
+        <v>2832</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>20.4</v>
+        <v>13.2</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>14.4</v>
+        <v>6.6</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>40.1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>4020</v>
+        <v>2900</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>22.1</v>
+        <v>6.2</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>26.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1405</v>
+        <v>1055</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>12.5</v>
+        <v>8.1</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>17.4</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>98656</v>
+        <v>67916</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>997.1</v>
+        <v>682.7</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>419.9</v>
+        <v>284.2</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>142.1</v>
+        <v>174.5</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1559.1</v>
+        <v>1141.5</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1063,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 세그먼트별 - 2026-08</t>
+          <t>소사업 세그먼트별 - 2026-09</t>
         </is>
       </c>
     </row>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9350</v>
+        <v>3850</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>78</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3170</v>
+        <v>1350</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>16.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="5">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>68</v>
+        <v>680</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>45.6</v>
+        <v>34.9</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3.1</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3440</v>
+        <v>880</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>28.7</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="7">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>900</v>
+        <v>370</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>45.6</v>
+        <v>34.9</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>780</v>
+        <v>600</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>755</v>
+        <v>500</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="11">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>45.6</v>
+        <v>34.9</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1920</v>
+        <v>956</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1360</v>
+        <v>750</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="14">
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>468.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="15">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1140</v>
+        <v>700</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>530</v>
+        <v>385</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="17">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="19">
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.6</v>
+        <v>29.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5650</v>
+        <v>4000</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>12.6</v>
+        <v>25.2</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>4400</v>
+        <v>3100</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>32.1</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="23">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>24.8</v>
+        <v>39</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1990</v>
+        <v>1550</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>13.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>19.4</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>12.8</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="26">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>90.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>0</v>
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2960</v>
+        <v>3450</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>17.1</v>
+        <v>12.8</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>50.7</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1821</v>
+        <v>2450</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>27.8</v>
+        <v>7.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>50.7</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5365</v>
+        <v>2500</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>30.4</v>
+        <v>22.6</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>163.2</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>3215</v>
+        <v>1850</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>15.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>51.1</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>22.6</v>
+        <v>42.5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2620</v>
+        <v>2100</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>50.4</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1600</v>
+        <v>1250</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="35">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>51.9</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="36">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1125</v>
+        <v>1050</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>880</v>
+        <v>730</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>3</v>
+        <v>11.4</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>42.4</v>
+        <v>45.4</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3570</v>
+        <v>1900</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>156.6</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2090</v>
+        <v>950</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>48.8</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="41">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2527</v>
+        <v>1500</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>62.5</v>
+        <v>50.1</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>158</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1490</v>
+        <v>900</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>25.7</v>
+        <v>16.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>38.2</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="44">
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>23.6</v>
+        <v>1440</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>79.7</v>
+        <v>60.3</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>38.3</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="46">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>24.2</v>
+        <v>38</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>26.6</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="47">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>34</v>
+        <v>2.6</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="48">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2900</v>
+        <v>1250</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>13.2</v>
+        <v>43.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>38.4</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1730</v>
+        <v>1350</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>14.2</v>
+        <v>31.9</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>24.6</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="50">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>35.9</v>
+        <v>27.3</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="51">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3045</v>
+        <v>2000</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>11.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>34.3</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2280</v>
+        <v>1570</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>11.1</v>
+        <v>7.7</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>25.3</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="53">
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>0</v>
+        <v>37.8</v>
       </c>
       <c r="E53" s="4" t="n">
         <v>0</v>
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1170</v>
+        <v>900</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>7.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2060</v>
+        <v>1650</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="56">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D56" s="4" t="n">
         <v>23.8</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="57">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>815</v>
+        <v>670</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>24.7</v>
+        <v>19.2</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>20.1</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1075</v>
+        <v>790</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>20.4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D59" s="4" t="n">
         <v>0</v>
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>14.3</v>
+        <v>17.3</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>15</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="61">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2350</v>
+        <v>2850</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2.7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2420</v>
+        <v>3000</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>39.4</v>
+        <v>36.7</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>95.3</v>
+        <v>110</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>550</v>
+        <v>430</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>37.1</v>
+        <v>30.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>20.4</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1790</v>
+        <v>1400</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>8.1</v>
+        <v>4.7</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>14.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1325</v>
+        <v>1002</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>30.2</v>
+        <v>3</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>40.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2380</v>
+        <v>1500</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1640</v>
+        <v>1400</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>22.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>925</v>
+        <v>600</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>12.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="71">
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2566,7 +2566,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>소사업 월별 누적 - 2026-08 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
+          <t>소사업 월별 누적 - 2026-09 (마감월=온북 실적, 당월=RM FCST / 백만, VAT제외)</t>
         </is>
       </c>
     </row>
@@ -2824,26 +2824,53 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>9월</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RM FCST</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>682.7</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>284.2</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>1141.5</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>11833.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>누계</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="7" t="n">
-        <v>6902.5</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>2397.4</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>1392.6</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>10692.5</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>10692.5</v>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="7" t="n">
+        <v>7585.3</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2681.6</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1567.1</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>11833.9</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>11833.9</v>
       </c>
     </row>
   </sheetData>
@@ -2872,7 +2899,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2911,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>전년 2025-08 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
+          <t>전년 2025-09 실당소사업 × FCST 객실수 (미운영 사업장은 2026-05 대체)</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2804,23 +2804,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RM FCST</t>
+          <t>온북</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>997.1</v>
+        <v>1009</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>419.9</v>
+        <v>427.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>142.1</v>
+        <v>142.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1559.1</v>
+        <v>1578.5</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10692.5</v>
+        <v>10711.9</v>
       </c>
     </row>
     <row r="11">
@@ -2847,7 +2847,7 @@
         <v>1141.5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11833.9</v>
+        <v>11853.3</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7585.3</v>
+        <v>7597.2</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2681.6</v>
+        <v>2688.9</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1567.1</v>
+        <v>1567.3</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11833.9</v>
+        <v>11853.3</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11833.9</v>
+        <v>11853.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2804,23 +2804,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>온북</t>
+          <t>RM FCST</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1009</v>
+        <v>997.1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>427.3</v>
+        <v>419.9</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>142.2</v>
+        <v>142.1</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1578.5</v>
+        <v>1559.1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10711.9</v>
+        <v>10692.5</v>
       </c>
     </row>
     <row r="11">
@@ -2847,7 +2847,7 @@
         <v>1141.5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11853.3</v>
+        <v>11833.9</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7597.2</v>
+        <v>7585.3</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2688.9</v>
+        <v>2681.6</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1567.3</v>
+        <v>1567.1</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11853.3</v>
+        <v>11833.9</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11853.3</v>
+        <v>11833.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -2804,23 +2804,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RM FCST</t>
+          <t>온북</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>997.1</v>
+        <v>1009</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>419.9</v>
+        <v>427.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>142.1</v>
+        <v>142.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1559.1</v>
+        <v>1578.5</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10692.5</v>
+        <v>10711.9</v>
       </c>
     </row>
     <row r="11">
@@ -2847,7 +2847,7 @@
         <v>1141.5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11833.9</v>
+        <v>11853.3</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7585.3</v>
+        <v>7597.2</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2681.6</v>
+        <v>2688.9</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1567.1</v>
+        <v>1567.3</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11833.9</v>
+        <v>11853.3</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11833.9</v>
+        <v>11853.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>989.4</v>
+        <v>990</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>369.2</v>
+        <v>369.6</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>182.2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1540.9</v>
+        <v>1541.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9133.4</v>
+        <v>9134.299999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2820,7 +2820,7 @@
         <v>1578.5</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10711.9</v>
+        <v>10712.8</v>
       </c>
     </row>
     <row r="11">
@@ -2847,7 +2847,7 @@
         <v>1141.5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11853.3</v>
+        <v>11854.3</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7597.2</v>
+        <v>7597.7</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2688.9</v>
+        <v>2689.3</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>1567.3</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11853.3</v>
+        <v>11854.3</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11853.3</v>
+        <v>11854.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5880</v>
+        <v>5766</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>60.1</v>
+        <v>58.6</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>12.5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>96.3</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="4">
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1342</v>
+        <v>1362</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3.4</v>
@@ -554,7 +554,7 @@
         <v>3.2</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1100</v>
+        <v>1050</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>9.4</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1709</v>
+        <v>1706</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>7.3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>17.5</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1085</v>
+        <v>920</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.2</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="8">
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>740</v>
+        <v>690</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0</v>
@@ -642,7 +642,7 @@
         <v>0.9</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="9">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7124</v>
+        <v>6822</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>100.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0.9</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>123.2</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2900</v>
+        <v>2750</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>20.5</v>
+        <v>19.2</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>14.8</v>
+        <v>14.2</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>35.3</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="11">
@@ -699,16 +699,16 @@
         <v>5900</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>44.1</v>
+        <v>43.5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>63.3</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4490</v>
+        <v>4471</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>56.4</v>
@@ -727,10 +727,10 @@
         <v>18.1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>80.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3352</v>
+        <v>3402</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>40.4</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1790</v>
+        <v>1724</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="15">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2850</v>
+        <v>2775</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>105.5</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2416</v>
+        <v>2296</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>75.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>23</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>113.2</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="17">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1289</v>
+        <v>1237</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>24.1</v>
+        <v>21.1</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>30.4</v>
@@ -840,7 +840,7 @@
         <v>0.2</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>54.8</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2610</v>
+        <v>2510</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>53.9</v>
+        <v>47.5</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>43.1</v>
+        <v>44.7</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>97.3</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>3570</v>
+        <v>3600</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>16.4</v>
+        <v>15.6</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2605</v>
+        <v>2554</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>1.3</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1527</v>
+        <v>1357</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>12.9</v>
+        <v>11.1</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>27.9</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6850</v>
+        <v>6700</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17.3</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>133.5</v>
+        <v>122.8</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2832</v>
+        <v>2837</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>13.2</v>
+        <v>15.4</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>22.9</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2900</v>
+        <v>2920</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1055</v>
+        <v>1130</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>12.8</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>67916</v>
+        <v>66479</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>682.7</v>
+        <v>650.8</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>284.2</v>
+        <v>285.7</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>174.5</v>
+        <v>163.5</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1141.5</v>
+        <v>1099.9</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3850</v>
+        <v>3750</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>60.1</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="4">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>34.9</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="6">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="7">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="11">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>468.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>700</v>
+        <v>570</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="17">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0.1</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>25.2</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>100.6</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="23">
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>39</v>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1550</v>
+        <v>1450</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>13.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20.5</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>14.8</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3450</v>
+        <v>3400</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>12.8</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>44.1</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2450</v>
+        <v>2500</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="29">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>42.5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="33">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1050</v>
+        <v>995</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>9.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>45.4</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="39">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>950</v>
+        <v>975</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="41">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>50.1</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>75.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>900</v>
+        <v>930</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>16.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>24.1</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="46">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>2.6</v>
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1250</v>
+        <v>1100</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>43.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>53.9</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>43.1</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>16.4</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1570</v>
+        <v>1700</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="53">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="D54" s="4" t="n">
         <v>5.7</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="55">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>2.9</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D56" s="4" t="n">
         <v>23.8</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>670</v>
+        <v>580</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>12.9</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="58">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>790</v>
+        <v>710</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>19</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="59">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2850</v>
+        <v>3000</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>2.1</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="62">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>36.7</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>30.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>13.2</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>4.7</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="65">
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>3</v>
@@ -2429,13 +2429,13 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1500</v>
+        <v>1420</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.1</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="67">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="68">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>13.5</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="71">
@@ -2835,19 +2835,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>682.7</v>
+        <v>650.8</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>284.2</v>
+        <v>285.7</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>174.5</v>
+        <v>163.5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1141.5</v>
+        <v>1099.9</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11854.3</v>
+        <v>11812.8</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7597.7</v>
+        <v>7565.8</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2689.3</v>
+        <v>2690.8</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1567.3</v>
+        <v>1556.2</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11854.3</v>
+        <v>11812.8</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11854.3</v>
+        <v>11812.8</v>
       </c>
     </row>
   </sheetData>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.08.25.pdf</t>
+          <t>Revenue Meeting_2026.09.01.pdf</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.08.25</t>
+          <t>2026.09.01</t>
         </is>
       </c>
     </row>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2835,19 +2835,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>650.8</v>
+        <v>682.7</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>285.7</v>
+        <v>284.2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>163.5</v>
+        <v>174.5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1099.9</v>
+        <v>1141.5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11812.8</v>
+        <v>11854.3</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7565.8</v>
+        <v>7597.7</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2690.8</v>
+        <v>2689.3</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1556.2</v>
+        <v>1567.3</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11812.8</v>
+        <v>11854.3</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11812.8</v>
+        <v>11854.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사업장별 소사업" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세그먼트별 상세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별 누적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메타정보" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2835,19 +2835,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>682.7</v>
+        <v>650.8</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>284.2</v>
+        <v>285.7</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>174.5</v>
+        <v>163.5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1141.5</v>
+        <v>1099.9</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11854.3</v>
+        <v>11812.8</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7597.7</v>
+        <v>7565.8</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2689.3</v>
+        <v>2690.8</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1567.3</v>
+        <v>1556.2</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11854.3</v>
+        <v>11812.8</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11854.3</v>
+        <v>11812.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/소사업_예상매출.xlsx
+++ b/data/소사업_예상매출.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5766</v>
+        <v>5316</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>58.6</v>
+        <v>50.8</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>23.2</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>94.3</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1362</v>
+        <v>1342</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>14.1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>3.2</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="5">
@@ -564,19 +564,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1050</v>
+        <v>930</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>13.5</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="6">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1706</v>
+        <v>1616</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>2.8</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>920</v>
+        <v>845</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="8">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>690</v>
+        <v>660</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.6</v>
@@ -642,7 +642,7 @@
         <v>0.9</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>6822</v>
+        <v>6323</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>95.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>20.9</v>
@@ -664,7 +664,7 @@
         <v>0.9</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>117.3</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="10">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2750</v>
+        <v>2350</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>19.2</v>
+        <v>16.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>14.2</v>
+        <v>12</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>33.5</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="11">
@@ -699,16 +699,16 @@
         <v>5900</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>43.5</v>
+        <v>38.4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>19.6</v>
+        <v>22.7</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>63.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="12">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4471</v>
+        <v>4247</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>56.4</v>
+        <v>51.9</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>79.59999999999999</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="13">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3402</v>
+        <v>3572</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>40.4</v>
+        <v>39.4</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="14">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1724</v>
+        <v>1684</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="15">
@@ -787,16 +787,16 @@
         <v>2775</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>79</v>
+        <v>76.8</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>101.7</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="16">
@@ -809,16 +809,16 @@
         <v>2296</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>15.6</v>
+        <v>17.2</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>23</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>106.2</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="17">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1237</v>
+        <v>1279</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>21.1</v>
+        <v>24.1</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>30.4</v>
@@ -840,7 +840,7 @@
         <v>0.2</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>51.8</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="18">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>2510</v>
+        <v>2560</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>47.5</v>
+        <v>51.8</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>44.7</v>
+        <v>43.1</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>0.3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>92.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>3600</v>
+        <v>3430</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>13.1</v>
+        <v>13.8</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>28.6</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="20">
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1357</v>
+        <v>1257</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>11.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>13.5</v>
@@ -928,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>24.6</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="22">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>6700</v>
+        <v>6500</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>17.3</v>
@@ -947,10 +947,10 @@
         <v>6.4</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>99</v>
+        <v>91.7</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>122.8</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2837</v>
+        <v>3029</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>15.4</v>
+        <v>16.3</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>24.8</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2920</v>
+        <v>2950</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.6</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="25">
@@ -1004,19 +1004,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1130</v>
+        <v>1200</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>13.7</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="26">
@@ -1026,19 +1026,19 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>66479</v>
+        <v>64615</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>650.8</v>
+        <v>610.7</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>285.7</v>
+        <v>290.8</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>163.5</v>
+        <v>157.1</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1099.9</v>
+        <v>1058.6</v>
       </c>
     </row>
   </sheetData>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>58.6</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="4">
@@ -1127,13 +1127,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="5">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>15.6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="10">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>950</v>
+        <v>880</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="13">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="14">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>570</v>
+        <v>520</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="16">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17">
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>2.1</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>3800</v>
+        <v>3300</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>25.2</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>95.59999999999999</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22">
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>39</v>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1450</v>
+        <v>1250</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>13.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>19.2</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="25">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>14.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3400</v>
+        <v>3000</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>12.8</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>43.5</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="28">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>7.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>19.6</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="29">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>22.6</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>56.4</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="31">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1850</v>
+        <v>1800</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="32">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>42.5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="33">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2100</v>
+        <v>2050</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>40.4</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="34">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1300</v>
+        <v>1520</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>3.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="35">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>995</v>
+        <v>925</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>9.6</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="D37" s="4" t="n">
         <v>11.4</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="38">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1800</v>
+        <v>1750</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>43.9</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>79</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="40">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>975</v>
+        <v>1025</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>23.4</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="41">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1350</v>
+        <v>1250</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>50.1</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="43">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>930</v>
+        <v>1030</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>16.7</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>15.6</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="44">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>60.3</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>21.1</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="46">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>2.6</v>
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>43.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>47.5</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="49">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>31.9</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>44.7</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="50">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1900</v>
+        <v>1630</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="52">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>7.7</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>13.1</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="53">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>580</v>
+        <v>480</v>
       </c>
       <c r="D57" s="4" t="n">
         <v>19.2</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>11.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>36.7</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>99</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="63">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>30.8</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>15.4</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="64">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1350</v>
+        <v>1550</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>4.7</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="65">
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>987</v>
+        <v>949</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="66">
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1420</v>
+        <v>1400</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>1.1</v>
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>4.4</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="68">
@@ -2513,13 +2513,13 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>480</v>
+        <v>550</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>10.2</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="71">
@@ -2835,19 +2835,19 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>650.8</v>
+        <v>610.7</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>285.7</v>
+        <v>290.8</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>163.5</v>
+        <v>157.1</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1099.9</v>
+        <v>1058.6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>11812.8</v>
+        <v>11771.4</v>
       </c>
     </row>
     <row r="12">
@@ -2858,19 +2858,19 @@
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="7" t="n">
-        <v>7565.8</v>
+        <v>7525.7</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2690.8</v>
+        <v>2695.9</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1556.2</v>
+        <v>1549.9</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>11812.8</v>
+        <v>11771.4</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>11812.8</v>
+        <v>11771.4</v>
       </c>
     </row>
   </sheetData>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revenue Meeting_2026.09.01.pdf</t>
+          <t>Revenue Meeting_2026.09.08.pdf</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026.09.01</t>
+          <t>2026.09.08</t>
         </is>
       </c>
     </row>
